--- a/workspaces/btc_daily_14days/stoch/stoch_7.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_7.xlsx
@@ -568,625 +568,625 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 4.61</t>
+          <t>X ≈ 4.636</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.847221020449368</v>
+        <v>6.37403036345777</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.939426704817599</v>
+        <v>2.554039624922474</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.6539982279181586</v>
+        <v>-0.05554850396080013</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.67562945578149</v>
+        <v>2.291182157060845</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.762889547352984</v>
+        <v>-8.222958110019398</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.66781853922068</v>
+        <v>-10.14590193207643</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.554315423464459</v>
+        <v>-8.014588877219893</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.822914791733375</v>
+        <v>-6.264100497997866</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.582714917251558</v>
+        <v>-2.997287215033076</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.435573743389675</v>
+        <v>-3.847419303952414</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.743581305507391</v>
+        <v>-5.163313119781826</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-11.22025120539394</v>
+        <v>-10.68303842699231</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-9.440313349219515</v>
+        <v>-8.884224881610805</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.192407755914658</v>
+        <v>-8.636774639646823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 7.92</t>
+          <t>X ≈ 7.946</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.387295624743942</v>
+        <v>4.371473418864497</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.858777480192494</v>
+        <v>1.852450886239453</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.217927486487639</v>
+        <v>4.203550812597037</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.431255018041696</v>
+        <v>3.41947967181634</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.2399137848597</v>
+        <v>10.20628334322234</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.865815477558506</v>
+        <v>6.84363135762338</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.026122198024332</v>
+        <v>4.013411730684268</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.559040834463822</v>
+        <v>3.547956654190855</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.933873626515073</v>
+        <v>9.901726683161108</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.245242088533665</v>
+        <v>7.221930536576394</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.961525068484775</v>
+        <v>7.935858026633113</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.917590338772413</v>
+        <v>8.889232849482568</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.577984546058879</v>
+        <v>7.554070169078024</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>10.59166660924812</v>
+        <v>10.55792464679558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 11.23</t>
+          <t>X ≈ 11.26</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>132</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.567167740395917</v>
+        <v>3.553162115651119</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.956137723667389</v>
+        <v>1.949070972603337</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.31964731988424</v>
+        <v>2.310897400306345</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.72520234863115</v>
+        <v>4.708212367461861</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.979350001050946</v>
+        <v>7.951364756431055</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.761969643308909</v>
+        <v>6.738725476408426</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.126058724185668</v>
+        <v>2.11908767396195</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.9354340029832</v>
+        <v>3.92234335092305</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.116390098125869</v>
+        <v>3.105696701859209</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.783742799722923</v>
+        <v>3.770877244246329</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.300693311082064</v>
+        <v>1.296353870228181</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9442347079301285</v>
+        <v>-0.9403986771430297</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6062322888373615</v>
+        <v>-0.6034539724497066</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.115994417297564</v>
+        <v>-1.111522114394305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 14.54</t>
+          <t>X ≈ 14.56</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.5834847567129273</v>
+        <v>0.5888896698966519</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.588326885967071</v>
+        <v>3.604952807003521</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.194350692860297</v>
+        <v>3.209859110967976</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.944921388908888</v>
+        <v>7.981773336790397</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.327938604590642</v>
+        <v>4.348972790246307</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4239086192116872</v>
+        <v>0.4267381433389801</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3414592970694272</v>
+        <v>0.3428226995465735</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.663978918884091</v>
+        <v>-1.671377383368402</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.267086889643764</v>
+        <v>-3.281145861825053</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.342394864887687</v>
+        <v>-3.356855514745462</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.233165358853</v>
+        <v>-1.238619882917085</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4269058305303375</v>
+        <v>-0.4297145592891454</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.616832750864219</v>
+        <v>-1.625003394548187</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.368726896288123</v>
+        <v>-1.375792727502123</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 17.86</t>
+          <t>X ≈ 17.88</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2546323500603833</v>
+        <v>0.4438751720997161</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.11927319734702</v>
+        <v>1.770820886641253</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.471354218943247</v>
+        <v>1.377291879882506</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.878979059432787</v>
+        <v>-2.159909111859349</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.418738586963613</v>
+        <v>-2.697338827716699</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6142457637268777</v>
+        <v>0.5346826183699989</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.207409703560302</v>
+        <v>-3.952078657372411</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.181294971705903</v>
+        <v>-2.951457128925725</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.0003173595210199665</v>
+        <v>-0.8105697248193096</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8518002883305797</v>
+        <v>-1.65993853352623</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.309154904629473</v>
+        <v>-0.3956732005010934</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.520520494525705</v>
+        <v>-3.300820542963905</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.8000017491831102</v>
+        <v>-0.04652929821602214</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.799592445981986</v>
+        <v>0.938388759045985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 21.16</t>
+          <t>X ≈ 21.19</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.468393740858552</v>
+        <v>2.134657685204132</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.433576310959644</v>
+        <v>-1.804073815625379</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1109538675178285</v>
+        <v>-0.2371029199563637</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.767511913550443</v>
+        <v>0.6657086329491122</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.586056070527853</v>
+        <v>-3.737575534374592</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.345344127529508</v>
+        <v>-5.760331572160226</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.450032905396938</v>
+        <v>1.890241715187912</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.808606316978839</v>
+        <v>5.293475362771559</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.454423633407423</v>
+        <v>2.911759932967641</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.449735135516292</v>
+        <v>-1.033535281252753</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.949468301966931</v>
+        <v>-4.336496551597264</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8534557400155549</v>
+        <v>-0.4295917245434353</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.803633870099311</v>
+        <v>-2.399903007117324</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.024427812408682</v>
+        <v>-0.6005989290525093</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 24.48</t>
+          <t>X ≈ 24.49</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.324743497971845</v>
+        <v>3.978732394505975</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.106182111044738</v>
+        <v>-4.473854502075369</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.016724535748999</v>
+        <v>-5.629087264388843</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-8.16212150947041</v>
+        <v>-7.784908928641975</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.428776961528307</v>
+        <v>-6.039089560983655</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6931324664319476</v>
+        <v>1.111691102341531</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6083223014638293</v>
+        <v>1.027866242735769</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.376723019379966</v>
+        <v>-0.9622876357420438</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.0797903609295787</v>
+        <v>0.5008037226085662</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.7725707794327761</v>
+        <v>-0.3478438361897176</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.9783059681842161</v>
+        <v>-0.5524871460330161</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.464036071148634</v>
+        <v>-2.044034768713203</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.646428642224024</v>
+        <v>-3.228033419618704</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.636545677987243</v>
+        <v>-2.216079134981854</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 27.79</t>
+          <t>X ≈ 27.8</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.743403785053331</v>
+        <v>4.016550085319111</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.816679168467978</v>
+        <v>1.745973956563496</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.68659178594045</v>
+        <v>6.563735233072393</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7.477557992263769</v>
+        <v>6.69699599506076</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.665814501793207</v>
+        <v>3.904932084431792</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.986828733071526</v>
+        <v>2.246031226357438</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.221644869411811</v>
+        <v>3.466882017110706</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.416766091285631</v>
+        <v>3.653935543895052</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.698006067327377</v>
+        <v>3.594039545432381</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.8766877934331774</v>
+        <v>0.788291104282969</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.332830246582134</v>
+        <v>1.23698513373381</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.04917005360551485</v>
+        <v>-0.03452364620540038</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.689090630042642</v>
+        <v>-1.761559577959659</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.198627872892196</v>
+        <v>1.101787451856438</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 31.09</t>
+          <t>X ≈ 31.12</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.169113995885802</v>
+        <v>-2.489310523173671</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.40269958736598</v>
+        <v>-1.398785993001042</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.257863752631998</v>
+        <v>2.247988984903088</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.065404619280265</v>
+        <v>3.726330091957237</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4979614984042229</v>
+        <v>1.842704870426005</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.823918998820446</v>
+        <v>4.161215355204753</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.769112220201244</v>
+        <v>6.100675994819348</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.273256564871119</v>
+        <v>3.613546542952442</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.536294376545847</v>
+        <v>1.530174953545725</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.007173939024440301</v>
+        <v>0.007609828195185742</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.188148657252349</v>
+        <v>3.17802018299794</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.190238272611118</v>
+        <v>1.187959731396688</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5870326061436799</v>
+        <v>-0.5827640938392804</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.691769682648449</v>
+        <v>-1.684822687694876</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 34.41</t>
+          <t>X ≈ 34.42</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-10.01556221401528</v>
+        <v>-10.11953154619849</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.778490808170325</v>
+        <v>-2.74551568275232</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3677868471771362</v>
+        <v>0.4511056875220163</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4986546261892215</v>
+        <v>0.5809839555639869</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.616232778088765</v>
+        <v>1.842155075694521</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.142703879567101</v>
+        <v>0.3421222282215126</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.058392033854794</v>
+        <v>0.257964554814869</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5909675042836042</v>
+        <v>-0.2078600573386993</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3562671495877723</v>
+        <v>-0.2687181817973681</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3224173428283308</v>
+        <v>-0.2172800818405278</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.414785493359872</v>
+        <v>-1.321976019841813</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.167817271175352</v>
+        <v>2.313246125105628</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8582523765990118</v>
+        <v>0.9932929592676558</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.10988362183808</v>
+        <v>1.243105240233056</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 37.72</t>
+          <t>X ≈ 37.73</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>139</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.133726089994148</v>
+        <v>-2.499654740272355</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4790261894257739</v>
+        <v>-0.865010234918941</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.281835450771354</v>
+        <v>1.607008262019185</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.289602903894348</v>
+        <v>4.606417991609156</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.757939284696121</v>
+        <v>4.070942403936925</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.493316975091012</v>
+        <v>5.802321360710565</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.251732272216621</v>
+        <v>3.567595709196738</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.509494353795006</v>
+        <v>3.820947243759598</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.729748678645613</v>
+        <v>3.043516993208506</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.167306421908542</v>
+        <v>1.478338906000687</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.684765008678923</v>
+        <v>1.992878245393179</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.9996663734687985</v>
+        <v>1.309272757312293</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.46827179000551</v>
+        <v>-4.144471206613019</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.8302700310564575</v>
+        <v>1.13940441710777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 41.02</t>
+          <t>X ≈ 41.03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.262669089440742</v>
+        <v>-2.908245057367076</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.797319625481919</v>
+        <v>-1.409200983982252</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.115503975613791</v>
+        <v>-0.2268199017050065</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.730508262096158</v>
+        <v>-5.170582816943366</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.414768767988704</v>
+        <v>-1.78808771306764</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.658076043885004</v>
+        <v>-3.059621503239669</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.280829124421501</v>
+        <v>-4.717691223576693</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.745700225031079</v>
+        <v>-5.189663301638689</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.57785485054896</v>
+        <v>-6.039237854079197</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.650485483530318</v>
+        <v>-6.114894700920885</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-10.48114138738409</v>
+        <v>-11.04372864338518</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.365014469497666</v>
+        <v>-7.867688564037522</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.612483000148366</v>
+        <v>-2.000049730723532</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.642009807595478</v>
+        <v>-9.170457929235624</v>
       </c>
     </row>
     <row r="18">
@@ -1199,150 +1199,150 @@
         <v>114</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.002210250034736</v>
+        <v>-5.986978830965327</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5962400033496706</v>
+        <v>-0.5944929708503182</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.868301692402405</v>
+        <v>-1.865832527008386</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.246820489619466</v>
+        <v>-5.234984172967351</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.276469774867273</v>
+        <v>-2.272101703705289</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2246418722393244</v>
+        <v>-0.2259626797595473</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5682284090505121</v>
+        <v>0.5653512963099061</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.654829542950772</v>
+        <v>-1.651058040243626</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.796539787619409</v>
+        <v>1.790660453258084</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.823416659866787</v>
+        <v>1.819341278162298</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.618480535918508</v>
+        <v>1.615476150038063</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.532203572765141</v>
+        <v>2.527195204645459</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5286603474778815</v>
+        <v>-0.5239228725079101</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.555735871778943</v>
+        <v>-5.537359434968458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 47.64</t>
+          <t>X ≈ 47.66</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.961107134335684</v>
+        <v>2.95095071266055</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.923193751356258</v>
+        <v>-5.905323479012985</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.590789730680115</v>
+        <v>-3.582924540760217</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.812190674654858</v>
+        <v>3.79802710118279</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.182860368673602</v>
+        <v>4.168299529666562</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.753029579116742</v>
+        <v>1.745658467341016</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9.854538058166476</v>
+        <v>9.823569956638018</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.20237679779607</v>
+        <v>1.197951626229155</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.409263414955745</v>
+        <v>-3.400113373398497</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.932512951704801</v>
+        <v>3.921729585599941</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.08430338478613209</v>
+        <v>0.08560634063443473</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.029554599381377</v>
+        <v>1.028567056402935</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.518484672486721</v>
+        <v>1.51754443211729</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.05457627522462616</v>
+        <v>-0.0509160537880291</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 50.95</t>
+          <t>X ≈ 50.97</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.820871948528563</v>
+        <v>-3.840929234502212</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7622447039943197</v>
+        <v>0.7649663277529655</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.252331749610107</v>
+        <v>1.265326445432294</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.382584882217408</v>
+        <v>1.398235393970147</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.499030923782207</v>
+        <v>3.526378777026807</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.56638436592285</v>
+        <v>5.606045333910316</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.007514704725672</v>
+        <v>-2.013947822393568</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.580619629943747</v>
+        <v>-1.588291553660135</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.640625173396693</v>
+        <v>-1.64950039102667</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.368353976476698</v>
+        <v>-3.390271554287793</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.684039630942195</v>
+        <v>-2.704048721747512</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.311229736912097</v>
+        <v>-5.348442077113361</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.066428272098364</v>
+        <v>-3.092845178272121</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1559815779662586</v>
+        <v>-0.164552417424801</v>
       </c>
     </row>
     <row r="21">
@@ -1355,358 +1355,358 @@
         <v>109</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.78701630186135</v>
+        <v>-4.774642051349375</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8940027588625128</v>
+        <v>-0.8906113669595541</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.288871465459103</v>
+        <v>-1.287903666596321</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.828343103493808</v>
+        <v>-4.818240313190294</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.697039547923559</v>
+        <v>-1.695433961418559</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.31702880286867</v>
+        <v>-2.313713477381349</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.236624905461838</v>
+        <v>-4.227211393912953</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1165742520867852</v>
+        <v>-0.1170427852091649</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.932588427507895</v>
+        <v>-2.924660560297809</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8077450656831999</v>
+        <v>0.8064248806573886</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6021398003692795</v>
+        <v>0.6024275730941042</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.042540719558012</v>
+        <v>-3.031103813421353</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.89324079827562</v>
+        <v>3.886184965895232</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.383864546095758</v>
+        <v>1.383612720190072</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 57.58</t>
+          <t>X ≈ 57.59</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>113</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.705827700740748</v>
+        <v>-4.692324603073004</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.532156208418691</v>
+        <v>2.525655460061515</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.402535507027451</v>
+        <v>-1.401119738336206</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.157238126632343</v>
+        <v>-2.154020356515623</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-8.005393854979054</v>
+        <v>-7.984704069649716</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.053084660626027</v>
+        <v>-5.041201734038012</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.022774130110491</v>
+        <v>-6.006963668056564</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.607657827611341</v>
+        <v>-5.59172152202234</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.899992256280939</v>
+        <v>-3.888285962750302</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.412667611232024</v>
+        <v>-7.389497588972418</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.509209292715781</v>
+        <v>-8.481582868590593</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-9.367749107319483</v>
+        <v>-9.336087304335166</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.4691081065398</v>
+        <v>-4.45188436916991</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-12.20721756998328</v>
+        <v>-12.16676480680513</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 60.88</t>
+          <t>X ≈ 60.89</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.028300810224728</v>
+        <v>4.015508042253856</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.40972263250265</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.572583128345201</v>
+        <v>0.5678318616980818</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.920352144844401</v>
+        <v>-2.914244704980767</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5602226352788051</v>
+        <v>-0.5607119761303778</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>-2.431632558521791</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.695340501792195</v>
+        <v>-4.681673910872249</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-6.615353578059114</v>
+        <v>-6.594027687059288</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.680209756338066</v>
+        <v>-6.657977934547638</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.262074095730732</v>
+        <v>-8.233049934793797</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.294547473537072</v>
+        <v>-6.270329707383837</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-11.35174250706424</v>
+        <v>-11.30943098683347</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-13.23376833394599</v>
+        <v>-13.18601288013551</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.895849983930866</v>
+        <v>-7.863827779743445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.19</t>
+          <t>X ≈ 64.2</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>107</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.026148600583909</v>
+        <v>-2.020049810039318</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.441460531305076</v>
+        <v>-6.419191898563852</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.967170359397095</v>
+        <v>-4.953666383814472</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.967758348285031</v>
+        <v>-2.960637385377851</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.506179563356994</v>
+        <v>-3.496676955967082</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.464159570620353</v>
+        <v>1.456605425790549</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.424312464409034</v>
+        <v>-1.41991044574258</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.827969642242323</v>
+        <v>-2.816603603445124</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.891206109768163</v>
+        <v>-2.87881334633888</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.809847174773317</v>
+        <v>-2.795394694027905</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2081761572165135</v>
+        <v>-0.2013658328335381</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7596163966347262</v>
+        <v>0.7664687074369851</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.3370004420322843</v>
+        <v>0.3450720446912072</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3505068328461505</v>
+        <v>-0.3397860622844178</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.5</t>
+          <t>X ≈ 67.52</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.493438320209876</v>
+        <v>-1.5952226721638</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.286830114992412</v>
+        <v>-1.419499099576008</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.863517003407182</v>
+        <v>-0.03828066537393227</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.08491794738223</v>
+        <v>1.870758322509879</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.180775994962772</v>
+        <v>-1.333765741263036</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.792424966337911</v>
+        <v>-1.928207852241968</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.48647768002607</v>
+        <v>3.327983051584617</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2917718223861669</v>
+        <v>0.1961653701565993</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6800593709511134</v>
+        <v>-0.7550553567841618</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.019700271088112</v>
+        <v>3.744001787057428</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.548622406814147</v>
+        <v>6.216339893921571</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.023045244755103</v>
+        <v>1.79236387001049</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.512692388597571</v>
+        <v>2.26429767887084</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.762831345902768</v>
+        <v>2.514019011146829</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 70.81</t>
+          <t>X ≈ 70.83</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.6315616797900248</v>
+        <v>0.261305533763931</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.761261933174232</v>
+        <v>-2.909956433268285</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.156130639770822</v>
+        <v>-2.52462054618929</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.025877507163322</v>
+        <v>-2.395328524626272</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.5607012777645082</v>
+        <v>0.2072519669360204</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.829356784519916</v>
+        <v>-4.203444766644367</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.13284050179211</v>
+        <v>-2.717197075077479</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.948170688530887</v>
+        <v>-5.535479980999703</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.320418866931497</v>
+        <v>-0.8876205513012394</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.304736449898257</v>
+        <v>2.978612800568179</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8161844085336156</v>
+        <v>-1.156628361969553</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7798802877495987</v>
+        <v>0.4505561133545939</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.3567982349029322</v>
+        <v>0.02863963612579568</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.9616934127110994</v>
+        <v>-1.296442181204128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 74.12</t>
+          <t>X ≈ 74.14</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2207110474827942</v>
+        <v>-0.5871890257909129</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.8566384348897174</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.015032154922338</v>
+        <v>-6.431536332437076</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.642354779890596</v>
+        <v>-7.066671223924253</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.877745691932461</v>
+        <v>-2.243097297997586</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.853031026944073</v>
+        <v>-4.243958918734087</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.937764744216352</v>
+        <v>-4.330832122174506</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.977252211349281</v>
+        <v>-4.372896851252769</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.76743249807032</v>
+        <v>-2.136824499529034</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.130783186010191</v>
+        <v>-4.522292225445547</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.81770181853927</v>
+        <v>-3.194185503433147</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.020857981685175</v>
+        <v>-2.39383621071854</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.203734240906712</v>
+        <v>-3.587350672777809</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.433379658619437</v>
+        <v>-1.799167802039989</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>174</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.253688116571702</v>
+        <v>3.24025141584567</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.791539790963704</v>
+        <v>2.783766761218793</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.775742708736338</v>
+        <v>-2.76486969020042</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.377498929618227</v>
+        <v>1.370897576077432</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.8390777145461215</v>
+        <v>0.833962306045521</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.136519652261782</v>
+        <v>1.131107054753159</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6723519960449806</v>
+        <v>-0.6682801650382046</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.0328783982769</v>
+        <v>4.023653583147834</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.248309192929618</v>
+        <v>2.245466133582688</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.8209969062894373</v>
+        <v>0.8257615214509713</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.03779275093155832</v>
+        <v>0.04719947330958263</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.5107720346436153</v>
+        <v>-0.4934228688071585</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2176954831427551</v>
+        <v>0.2322779744370465</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1090756082401043</v>
+        <v>-0.09271333696483453</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>161</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9227107481128627</v>
+        <v>0.9160740398765981</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6888628648511812</v>
+        <v>-0.682569308746011</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.748566565198047</v>
+        <v>5.72238722141433</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.878819697805689</v>
+        <v>5.848722092100218</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.203752520000528</v>
+        <v>7.166757799831721</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.637840420449038</v>
+        <v>5.609310119512358</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.037578752866352</v>
+        <v>8.001550212811118</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.191513366507131</v>
+        <v>8.159585616102852</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.650024681730152</v>
+        <v>5.630108426256456</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.423271082993608</v>
+        <v>5.407679020584247</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.465405326774196</v>
+        <v>6.447258046412145</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.10864572258626</v>
+        <v>12.07154135398301</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.821774186040436</v>
+        <v>9.795353579491668</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.823722461151689</v>
+        <v>8.802838886923226</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.604549431321054</v>
+        <v>-3.627177913517563</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2161230442854034</v>
+        <v>-0.2242994473382538</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.388769528659616</v>
+        <v>-3.41038210506602</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.480738618274437</v>
+        <v>-5.512215312191429</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6662683192830485</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.388384562297553</v>
+        <v>-2.396954219204737</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.028673835125474</v>
+        <v>-3.046714355689019</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.162523900573639</v>
+        <v>-0.1672429468245724</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.578846759586092</v>
+        <v>-1.597441583493051</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3566245689375052</v>
+        <v>0.3466645734668816</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4043873916799186</v>
+        <v>-0.4235257798175027</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.191114863369393</v>
+        <v>2.184009427799616</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.562756017461652</v>
+        <v>4.571681306478894</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.698265581578177</v>
+        <v>3.697807133137196</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.78811507784831</v>
+        <v>4.797181343983226</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.632852144495665</v>
+        <v>4.639507367957258</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.296235865083524</v>
+        <v>2.300558756886943</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.942443041143925</v>
+        <v>-1.9449680076549</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.966301149419962</v>
+        <v>-2.967595738484206</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2416747456849038</v>
+        <v>-0.2401605943152987</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.297282249364947</v>
+        <v>-1.2992810948802</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.764465648146391</v>
+        <v>-1.768811324717376</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1162820384868368</v>
+        <v>0.1140553452962862</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7206882584932615</v>
+        <v>0.7184836938950667</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.9984251341417831</v>
+        <v>0.9954973394466435</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.491428174433828</v>
+        <v>2.489930959365694</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.335427088128164</v>
+        <v>3.335726250299111</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.125092324637023</v>
+        <v>2.122032948429052</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>221</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-6.339592166363836</v>
+        <v>-6.318257088848988</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-5.688722340414053</v>
+        <v>-5.663384073172253</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.821147608096616</v>
+        <v>-3.807327290244565</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.23840578770627</v>
+        <v>-3.224594630471444</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.944247817258116</v>
+        <v>-6.922274550076665</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.741828503976819</v>
+        <v>-5.721898054436359</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-4.016607470117904</v>
+        <v>-3.99806332731729</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.126324805550979</v>
+        <v>-3.106458480331064</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.01990387725364684</v>
+        <v>-0.01224865479342441</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.390432842143156</v>
+        <v>1.394395911121691</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.906401964914735</v>
+        <v>3.902593179011703</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.302493151685411</v>
+        <v>0.3170668340946889</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.7913015929452243</v>
+        <v>0.8017895987153949</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.036943401709877</v>
+        <v>1.051510930991718</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.345271357209405</v>
+        <v>2.347678967308809</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.034773013062328</v>
+        <v>5.03825558057612</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1988053709536217</v>
+        <v>-0.2002981628424436</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.69488862186892</v>
+        <v>3.698444816602873</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.005929772388157</v>
+        <v>1.006894288972326</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2281028928995212</v>
+        <v>0.2270868372612611</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1433691756272637</v>
+        <v>0.1402989205463712</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.826723411254349</v>
+        <v>1.824190634880672</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.840992342276351</v>
+        <v>2.841467237846416</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.067515823919578</v>
+        <v>3.068060305060584</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.339104224998408</v>
+        <v>5.343219325520209</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.07585597674975</v>
+        <v>8.080305185568335</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.496041536043073</v>
+        <v>5.497888412461272</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.827259728614152</v>
+        <v>6.828690825818605</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>175</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.636295463067135</v>
+        <v>-5.573600114657502</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.676440504602809</v>
+        <v>-2.631395459557766</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.357023496913676</v>
+        <v>-1.323193748798218</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.6553417928776071</v>
+        <v>-0.6512969316898847</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.193763007949777</v>
+        <v>-1.180525280426338</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2465360726230301</v>
+        <v>0.2599576574731799</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.590373783922168</v>
+        <v>3.590557641248886</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.123190385140674</v>
+        <v>3.141759975138839</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.490761927529803</v>
+        <v>2.488555639609224</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.787469922397534</v>
+        <v>2.783493885359015</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.601395966717277</v>
+        <v>2.578740561041435</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.34269983014287</v>
+        <v>4.327409432672589</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.226358546927479</v>
+        <v>6.192869107441965</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.30077400454234</v>
+        <v>5.299733296861106</v>
       </c>
     </row>
   </sheetData>
@@ -2210,67 +2210,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 2.955</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4089~4102</t>
-        </is>
+          <t>X &gt; 2.982</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2018732300100794</v>
+        <v>-0.2135065962402081</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.003742029273951175</v>
+        <v>0.0169392863379656</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1096367373317975</v>
+        <v>-0.096367587806931</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.06369923197424754</v>
+        <v>-0.05044741931559571</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.0520213918304151</v>
+        <v>-0.03863207590890738</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.03408738007755829</v>
+        <v>-0.02076303451983108</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.01657356070789007</v>
+        <v>0.02993422348261987</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.07557133752163026</v>
+        <v>0.08906378872780607</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1990458273134621</v>
+        <v>0.2125866456897256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1442840846539823</v>
+        <v>0.1580225824683552</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1243347517969227</v>
+        <v>0.138121781141308</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1480610372400974</v>
+        <v>0.161848831904166</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1816920204702583</v>
+        <v>0.1955941886703556</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2496686635242824</v>
+        <v>0.2635297743562219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 6.265</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3998~4011</t>
-        </is>
+          <t>X &gt; 6.291</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3998</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.36180032469764</v>
@@ -2318,13 +2314,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 9.575</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3889~3902</t>
-        </is>
+          <t>X &gt; 9.601</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3889</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.494463435535458</v>
@@ -2372,13 +2366,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 12.89</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3757~3770</t>
-        </is>
+          <t>X &gt; 12.91</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3757</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.6366743944805293</v>
@@ -2426,13 +2418,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 16.2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3628~3640</t>
-        </is>
+          <t>X &gt; 16.22</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3628</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.6802515070231578</v>
@@ -2480,121 +2470,115 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 19.51</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3494~3506</t>
-        </is>
+          <t>X &gt; 19.53</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3492</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6965187537524784</v>
+        <v>-0.7240319275159166</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3532287662698081</v>
+        <v>-0.3796336859575646</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5044468498164818</v>
+        <v>-0.5021650486800198</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5871553404490797</v>
+        <v>-0.6135578127902903</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.482006460670668</v>
+        <v>-0.5080487222354861</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2702298570498201</v>
+        <v>-0.2677496416626823</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1461333628180057</v>
+        <v>0.1774803041524464</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1517618137121062</v>
+        <v>0.183388049111926</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02083174339555427</v>
+        <v>0.0524270282283652</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.07272038213268672</v>
+        <v>0.1048407307333221</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.05559827581736698</v>
+        <v>0.0592228827254786</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.33492822966506</v>
+        <v>0.3673145761839081</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2742097982247245</v>
+        <v>0.3068112774963652</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.2254017897877603</v>
+        <v>0.2578416261034633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 22.82</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3364~3375</t>
-        </is>
+          <t>X &gt; 22.84</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3363</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8193642461359048</v>
+        <v>-0.8336872828655686</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3112952763870354</v>
+        <v>-0.324994144855232</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5283335146967261</v>
+        <v>-0.5123324630735269</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6785513138635864</v>
+        <v>-0.6626286934029437</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4003381647028732</v>
+        <v>-0.3841685679785911</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.07324023647711897</v>
+        <v>-0.05706184236616707</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.0955227435356818</v>
+        <v>0.1117811599289595</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.02899274330357571</v>
+        <v>-0.01262778896779082</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.07362767515009239</v>
+        <v>-0.05725300290792745</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1318142111140261</v>
+        <v>0.1485072503723899</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2110541933550749</v>
+        <v>0.2278365630786183</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3810551333771031</v>
+        <v>0.3978827928933413</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3936757302396714</v>
+        <v>0.4106370707509512</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2739136943470939</v>
+        <v>0.2907702111808135</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 26.13</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3232~3243</t>
-        </is>
+          <t>X &gt; 26.15</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3232</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.028745134887743</v>
@@ -2642,121 +2626,115 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 29.44</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3081~3091</t>
-        </is>
+          <t>X &gt; 29.46</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3079</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.312590698081223</v>
+        <v>-1.279453211760639</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.253879247090083</v>
+        <v>-0.2513849901690506</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6487479536866729</v>
+        <v>-0.6462536967656405</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7600451180406296</v>
+        <v>-0.725312638358659</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3920241188039597</v>
+        <v>-0.3567043749727858</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2564468622148723</v>
+        <v>-0.2212319869817705</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1292783256263021</v>
+        <v>-0.09391470788413159</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1900587240267981</v>
+        <v>-0.1544201728588561</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2656495158550669</v>
+        <v>-0.2624342925924807</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1338064577137246</v>
+        <v>0.1378333506293927</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2066820099945588</v>
+        <v>0.2108903709978733</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.518874147004631</v>
+        <v>0.5232642108058343</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6686269641213016</v>
+        <v>0.6733885879614547</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3527309321372201</v>
+        <v>0.3571266991716939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 32.75</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2933~2943</t>
-        </is>
+          <t>X &gt; 32.77</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2931</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.219228330403659</v>
+        <v>-1.218361815619694</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1961064267160353</v>
+        <v>-0.1934473073238934</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7949180293017548</v>
+        <v>-0.7923976465735478</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9524224748613861</v>
+        <v>-0.9500970546284435</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4367804461389255</v>
+        <v>-0.467762910734983</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4113548294025193</v>
+        <v>-0.4425224020768255</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3756126106356419</v>
+        <v>-0.4067087795320745</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3139359454868398</v>
+        <v>-0.3446825658783368</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3562671495877723</v>
+        <v>-0.3529515796714477</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1401746577701317</v>
+        <v>0.144408949851595</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.05674756765879607</v>
+        <v>0.06106600655706984</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4851120367124935</v>
+        <v>0.489700602123655</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7317726034006782</v>
+        <v>0.7368176554832928</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4555464574475394</v>
+        <v>0.4602343447726014</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 36.06</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2820~2830</t>
-        </is>
+          <t>X &gt; 36.07</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2820</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.8679966240969037</v>
@@ -2804,67 +2782,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 39.37</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2682~2691</t>
-        </is>
+          <t>X &gt; 39.38</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2681</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8026170641713293</v>
+        <v>-0.7834011454887815</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.07305355338976938</v>
+        <v>-0.05296732350880262</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9510140474259643</v>
+        <v>-0.9682821267596751</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.284125648427263</v>
+        <v>-1.301572468115353</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.781654670190882</v>
+        <v>-0.7987143972076041</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.781610501991949</v>
+        <v>-0.7987808269147791</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6231947226920767</v>
+        <v>-0.6402809779825844</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.5494286624783769</v>
+        <v>-0.5663199556536256</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5156711630119517</v>
+        <v>-0.5325334665772132</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1065446246420692</v>
+        <v>0.09022439879343835</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.0344468659097501</v>
+        <v>0.01816998407741721</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3878735587104813</v>
+        <v>0.371709523189601</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.995062813847376</v>
+        <v>0.9792758401574204</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4087138018147769</v>
+        <v>0.3926090894758048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 42.68</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2554~2561</t>
-        </is>
+          <t>X &gt; 42.69</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2554</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.6777413268480075</v>
@@ -2912,13 +2886,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 45.99</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2440~2447</t>
-        </is>
+          <t>X &gt; 46</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2440</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.4296867877212094</v>
@@ -2966,13 +2938,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 49.3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2330~2337</t>
-        </is>
+          <t>X &gt; 49.31</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2330</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.5892876997564045</v>
@@ -3020,13 +2990,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 52.61</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2218~2224</t>
-        </is>
+          <t>X &gt; 52.62</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2218</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.4250929964689689</v>
@@ -3074,13 +3042,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 55.92</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2109~2115</t>
-        </is>
+          <t>X &gt; 55.93</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2109</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.200294112172152</v>
@@ -3128,13 +3094,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 59.23</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1996~2002</t>
-        </is>
+          <t>X &gt; 59.24</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1996</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.05401422724256832</v>
@@ -3182,13 +3146,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 62.54</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1858~1864</t>
-        </is>
+          <t>X &gt; 62.55</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1858</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2402194360898093</v>
@@ -3236,13 +3198,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 65.85</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1751~1757</t>
-        </is>
+          <t>X &gt; 65.86</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1751</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1314576713767366</v>
@@ -3290,121 +3250,115 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 69.16</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1641~1647</t>
-        </is>
+          <t>X &gt; 69.17</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1639</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.02629452739171967</v>
+        <v>-0.03143224118262111</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6612297183133222</v>
+        <v>0.6062342674336705</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.765818708987581</v>
+        <v>-0.822069089618843</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8784313930163918</v>
+        <v>-0.9349770512362738</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4453893415433257</v>
+        <v>-0.5007538894087418</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7551119454184416</v>
+        <v>-0.8112146872553865</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2933975752590214</v>
+        <v>-0.2880456689653599</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.730550218502934</v>
+        <v>0.7377194084288163</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.068269526313991</v>
+        <v>1.075928434790043</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.590584604858492</v>
+        <v>1.539018506900689</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.664385287586953</v>
+        <v>1.613127259047886</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.012984515324398</v>
+        <v>2.96329793441474</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.933532466021227</v>
+        <v>2.884231436388184</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.061376893970888</v>
+        <v>3.011927143283145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 72.47</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1513~1519</t>
-        </is>
+          <t>X &gt; 72.48</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1512</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.02470889295521062</v>
+        <v>-0.05602066540101447</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.8653633136987082</v>
+        <v>0.9015756821090335</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6486627332533743</v>
+        <v>-0.6790637754756901</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7817407395530509</v>
+        <v>-0.8123152541988929</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5301685379036982</v>
+        <v>-0.5602226352789756</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4960577390952139</v>
+        <v>-0.5262853088940105</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.05412917855313992</v>
+        <v>-0.08400980350489107</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.293339077028499</v>
+        <v>1.264634965609645</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.269554657542052</v>
+        <v>1.240856160473633</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.446139946421965</v>
+        <v>1.418100203133655</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.873412885416734</v>
+        <v>1.845772076421703</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.201159196779024</v>
+        <v>3.174354952453527</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.1506634611385</v>
+        <v>3.124086038658902</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.400384793414787</v>
+        <v>3.373807370935189</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 75.78</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1382~1387</t>
-        </is>
+          <t>X &gt; 75.79</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1382</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.006055479546674292</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 79.09</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1208~1213</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1208</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.473652664810146</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 82.4</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1047~1052</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1047</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.6873546700198574</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 85.71</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>869~872</t>
-        </is>
+      <c r="B31" t="n">
+        <v>869</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.08518143947602397</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 89.02</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>664~666</t>
-        </is>
+      <c r="B32" t="n">
+        <v>664</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.592537419309075</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 92.33</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>443~445</t>
-        </is>
+      <c r="B33" t="n">
+        <v>443</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.7649886460821662</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 95.64</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>258~259</t>
-        </is>
+      <c r="B34" t="n">
+        <v>258</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.369886196657859</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 98.95</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>10.60179977502812</v>
@@ -3964,67 +3904,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 2.955</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+          <t>X &lt; 2.982</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.952344812320142</v>
+        <v>9.41132358455193</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.316674813813719</v>
+        <v>0.656892828730534</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.536263938542433</v>
+        <v>3.833452693562514</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.461697794041491</v>
+        <v>2.773229635693816</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.923276578969322</v>
+        <v>2.234808420621647</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.220718516684983</v>
+        <v>2.532250358337308</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.931165522304283</v>
+        <v>1.257040450588846</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.9456564306940933</v>
+        <v>-1.591095329145041</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.825933425310133</v>
+        <v>-6.413999977232102</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.06160077901275</v>
+        <v>-3.692696590831453</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.061534826221902</v>
+        <v>-2.706973724672849</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.231970945984898</v>
+        <v>-3.863066757803601</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.857044834038241</v>
+        <v>-5.4737975592247</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.22178133308725</v>
+        <v>-8.795504798376989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 6.265</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>174~174</t>
-        </is>
+          <t>X &lt; 6.291</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>174</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.851389265996922</v>
@@ -4072,13 +4008,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 9.575</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>283~283</t>
-        </is>
+          <t>X &lt; 9.601</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>283</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6.517162386503806</v>
@@ -4126,13 +4060,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 12.89</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>415~415</t>
-        </is>
+          <t>X &lt; 12.91</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>415</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>5.578850836416535</v>
@@ -4180,13 +4112,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 16.2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>544~545</t>
-        </is>
+          <t>X &lt; 16.22</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>544</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.387295624744155</v>
@@ -4234,121 +4164,115 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 19.51</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>678~679</t>
-        </is>
+          <t>X &lt; 19.53</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>680</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.471215582588258</v>
+        <v>3.600541121787089</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.006917374631364</v>
+        <v>2.135810386943248</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.495701098078953</v>
+        <v>2.475156070948707</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.067780445708543</v>
+        <v>3.192780716037852</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.529359230636373</v>
+        <v>2.654359500965683</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.584083480966896</v>
+        <v>1.565863803715466</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4180543660988931</v>
+        <v>-0.5776934429685809</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4427598887741979</v>
+        <v>-0.6037003711618496</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3811959772558922</v>
+        <v>0.2176526838323269</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1210412937028877</v>
+        <v>-0.04423720707795553</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2112732201227701</v>
+        <v>0.1921859391926972</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.229269876219114</v>
+        <v>-1.391077962285394</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.912061360320358</v>
+        <v>-1.076038455583237</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.6623400280440706</v>
+        <v>-0.82631712330695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 22.82</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>808~810</t>
-        </is>
+          <t>X &lt; 22.84</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>809</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.309030815592493</v>
+        <v>3.363528387558212</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.505345650056341</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.113221956026457</v>
+        <v>2.043329236772387</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.861522060203804</v>
+        <v>2.790866319997171</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.705053873561788</v>
+        <v>1.635161154307717</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.463650641222749</v>
+        <v>0.3955736851958633</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1161325810000235</v>
+        <v>-0.1835976093322884</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4067830301194633</v>
+        <v>0.3380941463979639</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7170702726500338</v>
+        <v>0.6479224431575545</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1330549123778937</v>
+        <v>-0.2022027418703729</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4615706129330945</v>
+        <v>-0.5305654605019114</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.169761713013408</v>
+        <v>-1.237838669040293</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.218729195245437</v>
+        <v>-1.287265097043289</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7214831104939066</v>
+        <v>-0.7903249761390683</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 26.13</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>940~942</t>
-        </is>
+          <t>X &lt; 26.15</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>940</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3.451359981276227</v>
@@ -4396,121 +4320,115 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 29.44</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1091~1094</t>
-        </is>
+          <t>X &lt; 29.46</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1093</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.630876122203183</v>
+        <v>3.528459490009006</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.831002692054291</v>
+        <v>0.821995366095841</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.767273980540246</v>
+        <v>1.755827122786251</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.172001038124883</v>
+        <v>2.068728657220241</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.135907321720552</v>
+        <v>1.033450363687727</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.8431054061309524</v>
+        <v>0.7416347525341536</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5750536320300697</v>
+        <v>0.4739184186104524</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7494834321486579</v>
+        <v>0.6471741781089122</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.055119659623564</v>
+        <v>1.043630833555156</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.06998261064726563</v>
+        <v>-0.08096827644990157</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.2747359349648448</v>
+        <v>-0.2857216007674808</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.156943061762405</v>
+        <v>-1.166251526679133</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.577197672707307</v>
+        <v>-1.586506137624035</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6858631415309304</v>
+        <v>-0.6963456470677869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 32.75</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1239~1242</t>
-        </is>
+          <t>X &lt; 32.77</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1241</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.820571341625772</v>
+        <v>2.812027917732152</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.5648753454086943</v>
+        <v>0.5573674880476318</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.8256632764258</v>
+        <v>1.815485410108501</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.278237118138854</v>
+        <v>2.267540634429601</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.05969321324838</v>
+        <v>1.130598620759685</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.079465854705354</v>
+        <v>1.150875890742057</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.075442387634851</v>
+        <v>1.146722350746167</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9310999896604457</v>
+        <v>1.001859661070228</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.112230854083471</v>
+        <v>1.10202012944071</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.06073533175155887</v>
+        <v>-0.07042576469278572</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1380625949397469</v>
+        <v>0.1277217973715921</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8767875003379118</v>
+        <v>-0.8854373498760566</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.458462611686365</v>
+        <v>-1.466852315373735</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.8051900284011921</v>
+        <v>-0.8142300967154981</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 36.06</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1352~1355</t>
-        </is>
+          <t>X &lt; 36.07</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1352</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.750104115214377</v>
@@ -4558,67 +4476,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 39.37</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1490~1494</t>
-        </is>
+          <t>X &lt; 39.38</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1491</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.388757128250539</v>
+        <v>1.352715525943871</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2151488169932136</v>
+        <v>0.1787899409890841</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.666339199371272</v>
+        <v>1.695698730624358</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.332785361469391</v>
+        <v>2.361785754725496</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.429979446778596</v>
+        <v>1.459243502965577</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.496775765815741</v>
+        <v>1.526214141033492</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.277813860624001</v>
+        <v>1.307342261454039</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.146200931641154</v>
+        <v>1.175504268440477</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.152315139418583</v>
+        <v>1.181573463411759</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.03373357855173253</v>
+        <v>0.06317195376948348</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1645507240328072</v>
+        <v>0.1937640352198429</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4722070582190767</v>
+        <v>-0.4425436189706033</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.563602608761293</v>
+        <v>-1.533489041451396</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5085121489682223</v>
+        <v>-0.4789387353320436</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 42.68</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1618~1624</t>
-        </is>
+          <t>X &lt; 42.69</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1618</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.016413896538793</v>
@@ -4666,13 +4580,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 45.99</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1732~1738</t>
-        </is>
+          <t>X &lt; 46</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1732</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.5560438431962353</v>
@@ -4720,13 +4632,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 49.3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1842~1848</t>
-        </is>
+          <t>X &lt; 49.31</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1842</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.6992023724307188</v>
@@ -4774,13 +4684,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 52.61</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1954~1961</t>
-        </is>
+          <t>X &lt; 52.62</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1954</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.4387391402693694</v>
@@ -4828,13 +4736,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 55.92</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2063~2070</t>
-        </is>
+          <t>X &lt; 55.93</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2063</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.1635665107079021</v>
@@ -4882,13 +4788,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 59.23</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2176~2183</t>
-        </is>
+          <t>X &lt; 59.24</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2176</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.08849100000841759</v>
@@ -4936,13 +4840,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 62.54</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2314~2321</t>
-        </is>
+          <t>X &lt; 62.55</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2314</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.1562816280881734</v>
@@ -4990,13 +4892,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 65.85</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2421~2428</t>
-        </is>
+          <t>X &lt; 65.86</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2421</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.0601036896747047</v>
@@ -5044,121 +4944,115 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 69.16</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2531~2538</t>
-        </is>
+          <t>X &lt; 69.17</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2533</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.05056991989476245</v>
+        <v>-0.01312335958004951</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.380140037234149</v>
+        <v>-0.3436885775223999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4685736189042586</v>
+        <v>0.5040594705522707</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5810628281423931</v>
+        <v>0.6165766709998692</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3011067631630837</v>
+        <v>0.3364307730326459</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5413868988595638</v>
+        <v>0.5767699413184317</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2809628157434361</v>
+        <v>0.2770351888156242</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3836929369085311</v>
+        <v>-0.3874647056249145</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5631762354130956</v>
+        <v>-0.5668544892026404</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.8998733003778412</v>
+        <v>-0.864493486385264</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9466487415990485</v>
+        <v>-0.9113936141756085</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.820638412057718</v>
+        <v>-1.784666336861754</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.766959373713526</v>
+        <v>-1.731361358224959</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.851138746938631</v>
+        <v>-1.815263037243</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 72.47</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2659~2666</t>
-        </is>
+          <t>X &lt; 72.48</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2660</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.01781941548379251</v>
+        <v>0</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4464753478083736</v>
+        <v>-0.4666023307736253</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3424617025715193</v>
+        <v>0.3594064146381797</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4557573970800135</v>
+        <v>0.4727148351790191</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.3135891440304661</v>
+        <v>0.3304041504644673</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3311444368255252</v>
+        <v>0.3480709014305745</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1166895733958597</v>
+        <v>0.133671147963625</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6512457050848894</v>
+        <v>-0.6341511083902205</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5994636363799728</v>
+        <v>-0.5824114229829007</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.697709122159786</v>
+        <v>-0.6809394640799624</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9400564314397641</v>
+        <v>-0.9232726455940892</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.695146958304861</v>
+        <v>-1.67806648937605</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.664273749700882</v>
+        <v>-1.647362813962452</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.807557306480632</v>
+        <v>-1.790492267048663</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 75.78</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2790~2798</t>
-        </is>
+          <t>X &lt; 75.79</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2790</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.0273911436552865</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 79.09</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2964~2972</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2964</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1647043446621694</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 82.4</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3125~3133</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3125</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.2036571154746767</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 85.71</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3303~3313</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3303</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.003248160234115005</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 89.02</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3508~3519</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3508</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.2772351665760482</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 92.33</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3729~3740</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3729</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1137591758249457</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 95.64</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3914~3926</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3914</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.002740997161396308</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 98.95</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4089~4101</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4089</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.2378908927532564</v>

--- a/workspaces/btc_daily_14days/stoch/stoch_7.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 4.636</t>
+          <t>X ≈ 4.638</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>90</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.37403036345777</v>
+        <v>6.386516694854684</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.554039624922474</v>
+        <v>2.566911849861903</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05554850396080013</v>
+        <v>-0.04257774369965972</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.291182157060845</v>
+        <v>2.304129705265616</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.222958110019398</v>
+        <v>-8.209881968266615</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.14590193207643</v>
+        <v>-10.13289069417295</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.014588877219893</v>
+        <v>-8.001549485025812</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.264100497997866</v>
+        <v>-6.250942082764631</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.997287215033076</v>
+        <v>-2.984106387777111</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.847419303952414</v>
+        <v>-3.834028905611753</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.163313119781826</v>
+        <v>-5.149867155195388</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.68303842699231</v>
+        <v>-10.66959438639729</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-8.884224881610805</v>
+        <v>-8.870672878573522</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.636774639646823</v>
+        <v>-8.647204275344471</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 7.946</t>
+          <t>X ≈ 7.947</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.371473418864497</v>
+        <v>4.383956482597895</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.852450886239453</v>
+        <v>1.865320739442012</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.203550812597037</v>
+        <v>4.216522807082775</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.41947967181634</v>
+        <v>3.432426428664627</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.20628334322234</v>
+        <v>10.21936841257149</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.84363135762338</v>
+        <v>6.856649679199023</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.013411730684268</v>
+        <v>4.026455121723529</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.547956654190855</v>
+        <v>3.561117675704189</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.901726683161108</v>
+        <v>9.9149108003093</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.221930536576394</v>
+        <v>7.235323053329211</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.935858026633113</v>
+        <v>7.949305955445766</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.889232849482568</v>
+        <v>8.902678983211054</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.554070169078024</v>
+        <v>7.567623021776953</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>10.55792464679558</v>
+        <v>10.54749501109743</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>132</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.553162115651119</v>
+        <v>3.565642190778242</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.949070972603337</v>
+        <v>1.961938452791685</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.310897400306345</v>
+        <v>2.323865884816044</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.708212367461861</v>
+        <v>4.721158117500181</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.951364756431055</v>
+        <v>7.964447141852617</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.738725476408426</v>
+        <v>6.751742398576241</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.11908767396195</v>
+        <v>2.132128780670186</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.92234335092305</v>
+        <v>3.935503338698275</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.105696701859209</v>
+        <v>3.118877689797635</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.770877244246329</v>
+        <v>3.784268098750601</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.296353870228181</v>
+        <v>1.309799890321628</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9403986771430297</v>
+        <v>-0.9269542551714096</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6034539724497066</v>
+        <v>-0.5899018707350976</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.111522114394305</v>
+        <v>-1.121951750092798</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>129</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.5888896698966519</v>
+        <v>0.6014740000252345</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.604952807003521</v>
+        <v>3.617933096461414</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.209859110967976</v>
+        <v>3.222940549524239</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.981773336790397</v>
+        <v>7.994833536517888</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.348972790246307</v>
+        <v>4.362166550883032</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4267381433389801</v>
+        <v>0.0191811478115298</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3428226995465735</v>
+        <v>0.3558611328024597</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.671377383368402</v>
+        <v>-1.658221330361009</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.281145861825053</v>
+        <v>-3.267968489542064</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.356855514745462</v>
+        <v>-3.343467770366736</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.238619882917085</v>
+        <v>-1.225175230265087</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4297145592891454</v>
+        <v>-0.4162706369462938</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.625003394548187</v>
+        <v>-1.611451658260599</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.375792727502123</v>
+        <v>-1.386222363200275</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>136</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4438751720997161</v>
+        <v>0.07699569263836281</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.770820886641253</v>
+        <v>1.783686152723696</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.377291879882506</v>
+        <v>1.390258075153071</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.159909111859349</v>
+        <v>-2.146968998321128</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.697338827716699</v>
+        <v>-2.68426352922112</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.5346826183699989</v>
+        <v>0.5479466922439826</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.952078657372411</v>
+        <v>-3.939044777485634</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.951457128925725</v>
+        <v>-2.938303654772341</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8105697248193096</v>
+        <v>-0.7973930552505308</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.65993853352623</v>
+        <v>-1.646551629050087</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3956732005010934</v>
+        <v>-0.3822293211077863</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.300820542963905</v>
+        <v>-3.287377733103405</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.04652929821602214</v>
+        <v>-0.03297777054122264</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.938388759045985</v>
+        <v>0.9279591233479962</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.134657685204132</v>
+        <v>2.148030016393889</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.804073815625379</v>
+        <v>-1.791092199792317</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2371029199563637</v>
+        <v>-0.64140897547923</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6657086329491122</v>
+        <v>0.6786478324478011</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.737575534374592</v>
+        <v>-3.724503872891148</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.760331572160226</v>
+        <v>-5.748921914620048</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.890241715187912</v>
+        <v>1.903276471247267</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.293475362771559</v>
+        <v>5.306630915447407</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.911759932967641</v>
+        <v>2.924936481471384</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.033535281252753</v>
+        <v>-1.020149634914389</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.336496551597264</v>
+        <v>-4.323054780872418</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4295917245434353</v>
+        <v>-0.4161492009863395</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.399903007117324</v>
+        <v>-2.386352045537144</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.6110285647508391</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>131</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.978732394505975</v>
+        <v>3.992743675418495</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.473854502075369</v>
+        <v>-4.460997801425847</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.629087264388843</v>
+        <v>-5.617663287303557</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-7.784908928641975</v>
+        <v>-7.771980106004591</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.039089560983655</v>
+        <v>-6.026022988050492</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.111691102341531</v>
+        <v>1.125095617740122</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.027866242735769</v>
+        <v>1.040897983202903</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.9622876357420438</v>
+        <v>-0.9491374855726988</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5008037226085662</v>
+        <v>0.5139774430237338</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3478438361897176</v>
+        <v>-0.3344595261004955</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5524871460330161</v>
+        <v>-0.5390456345909982</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.044034768713203</v>
+        <v>-2.03059335059816</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.228033419618704</v>
+        <v>-3.214482966082926</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.216079134981854</v>
+        <v>-2.226508770680006</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>153</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.016550085319111</v>
+        <v>4.030710989876262</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.745973956563496</v>
+        <v>1.758945509249344</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.563735233072393</v>
+        <v>6.57897317789655</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.69699599506076</v>
+        <v>6.710046513693925</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.904932084431792</v>
+        <v>3.562381494985743</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.246031226357438</v>
+        <v>2.259837508547193</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.466882017110706</v>
+        <v>3.479912437881829</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.653935543895052</v>
+        <v>3.667085716410256</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.594039545432381</v>
+        <v>3.607212616734074</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.788291104282969</v>
+        <v>0.8016739575402809</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.23698513373381</v>
+        <v>1.250425735213732</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.03452364620540038</v>
+        <v>-0.02108285149372335</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.761559577959659</v>
+        <v>-1.74800951907531</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.101787451856438</v>
+        <v>1.091357816158286</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.489310523173671</v>
+        <v>-2.477201013201622</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.398785993001042</v>
+        <v>-1.385930732639778</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.247988984903088</v>
+        <v>2.261983575441057</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.726330091957237</v>
+        <v>3.739266096804464</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.842704870426005</v>
+        <v>1.856566070312638</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.161215355204753</v>
+        <v>4.1757534570066</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.100675994819348</v>
+        <v>6.11370515539992</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.613546542952442</v>
+        <v>3.62669377520254</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.530174953545725</v>
+        <v>1.543344404136626</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.007609828195185742</v>
+        <v>0.02099006315086172</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.17802018299794</v>
+        <v>3.191459782835025</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.187959731396688</v>
+        <v>1.201399619166224</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5827640938392804</v>
+        <v>-0.5692145386765759</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.684822687694876</v>
+        <v>-1.695252323393028</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>111</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-10.11953154619849</v>
+        <v>-10.11016569969016</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.74551568275232</v>
+        <v>-2.732667047800227</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4511056875220163</v>
+        <v>0.4645537775687387</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5809839555639869</v>
+        <v>0.5939132514536851</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.842155075694521</v>
+        <v>1.856084999923084</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3421222282215126</v>
+        <v>0.3554433672925086</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.257964554814869</v>
+        <v>0.2709856702437534</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.2078600573386993</v>
+        <v>-0.1947185451041449</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2687181817973681</v>
+        <v>-0.2555524447067086</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.2172800818405278</v>
+        <v>-0.2039022477783448</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.321976019841813</v>
+        <v>-1.3085396392025</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.313246125105628</v>
+        <v>2.326685172593571</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.9932929592676558</v>
+        <v>1.006842102774051</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.243105240233056</v>
+        <v>1.232675604534904</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>139</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.499654740272355</v>
+        <v>-2.487741051162182</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.865010234918941</v>
+        <v>-1.239728302608427</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.607008262019185</v>
+        <v>1.62092861697915</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.606417991609156</v>
+        <v>4.619347270820576</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.070942403936925</v>
+        <v>4.085780036964813</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.802321360710565</v>
+        <v>5.817705073383408</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.567595709196738</v>
+        <v>3.580615898804645</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.820947243759598</v>
+        <v>3.834088446929663</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.043516993208506</v>
+        <v>3.056681963904659</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.478338906000687</v>
+        <v>1.491715123753664</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.992878245393179</v>
+        <v>2.006314009200814</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.309272757312293</v>
+        <v>1.322710337340418</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.144471206613019</v>
+        <v>-4.130923417408752</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.13940441710777</v>
+        <v>1.128974781409617</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.908245057367076</v>
+        <v>-2.879122424629799</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.409200983982252</v>
+        <v>-1.38569559893353</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2268199017050065</v>
+        <v>-0.2196054439209476</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.170582816943366</v>
+        <v>-5.540738217343332</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.78808771306764</v>
+        <v>-1.767247429662632</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.059621503239669</v>
+        <v>-3.028915789161481</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.717691223576693</v>
+        <v>-4.671245469423766</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.189663301638689</v>
+        <v>-5.138618142394556</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.039237854079197</v>
+        <v>-5.980922671096693</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.114894700920885</v>
+        <v>-6.050637959042049</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-11.04372864338518</v>
+        <v>-10.93958254027056</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.867688564037522</v>
+        <v>-7.786684115393193</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.000049730723532</v>
+        <v>-1.96206914567685</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-9.170457929235624</v>
+        <v>-8.768732053122754</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>114</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.986978830965327</v>
+        <v>-5.974456541289705</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5944929708503182</v>
+        <v>-0.581583161274267</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.865832527008386</v>
+        <v>-1.852825395590784</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.234984172967351</v>
+        <v>-5.222005030568887</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.272101703705289</v>
+        <v>-2.25899089933035</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2259626797595473</v>
+        <v>-0.2129197834651819</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5653512963099061</v>
+        <v>0.5779471041158217</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.651058040243626</v>
+        <v>-1.637392100692665</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.790660453258084</v>
+        <v>1.8029770805217</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.819341278162298</v>
+        <v>1.832129029063132</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.615476150038063</v>
+        <v>1.628477472242857</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.527195204645459</v>
+        <v>2.539914325930702</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5239228725079101</v>
+        <v>-0.5096995875829009</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.537359434968458</v>
+        <v>-5.54778907066661</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.95095071266055</v>
+        <v>2.963473002336173</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.905323479012985</v>
+        <v>-5.892413669436934</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.582924540760217</v>
+        <v>-3.569917409342615</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.79802710118279</v>
+        <v>3.811006243581254</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.168299529666562</v>
+        <v>4.181410334041502</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.745658467341016</v>
+        <v>1.758701363635382</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9.823569956638018</v>
+        <v>9.832159089786003</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.197951626229155</v>
+        <v>1.210444455639283</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.400113373398497</v>
+        <v>-3.385658338936864</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.921729585599941</v>
+        <v>3.93355731906243</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.08560634063443473</v>
+        <v>0.09921963548909929</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.028567056402935</v>
+        <v>1.041858389799309</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.51754443211729</v>
+        <v>1.530956045714859</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.0509160537880291</v>
+        <v>-0.06134568948618124</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>112</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.840929234502212</v>
+        <v>-3.82840694482659</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7649663277529655</v>
+        <v>0.7778761373290166</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.265326445432294</v>
+        <v>1.278333576849896</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.398235393970147</v>
+        <v>1.411214536368611</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.526378777026807</v>
+        <v>3.539489581401746</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.606045333910316</v>
+        <v>5.619088230204682</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.013947822393568</v>
+        <v>-2.479126166287003</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.588291553660135</v>
+        <v>-1.574614611280332</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.64950039102667</v>
+        <v>-1.63570739677165</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.390271554287793</v>
+        <v>-3.375310688678212</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.704048721747512</v>
+        <v>-2.689163798205101</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.348442077113361</v>
+        <v>-5.33229431261244</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.092845178272121</v>
+        <v>-3.077370326486886</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.164552417424801</v>
+        <v>-0.1749820531229531</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>109</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.774642051349375</v>
+        <v>-4.762119761673752</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8906113669595541</v>
+        <v>-0.877701557383503</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.287903666596321</v>
+        <v>-1.274896535178719</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.818240313190294</v>
+        <v>-4.80526117079183</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.695433961418559</v>
+        <v>-1.682323157043619</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.313713477381349</v>
+        <v>-2.300670581086983</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.227211393912953</v>
+        <v>-4.214145139612476</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1170427852091649</v>
+        <v>-0.1040096478203196</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.924660560297809</v>
+        <v>-2.910202244098571</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8064248806573886</v>
+        <v>0.8195623301065069</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6024275730941042</v>
+        <v>0.615896317611714</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.031103813421353</v>
+        <v>-3.015771604636349</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.886184965895232</v>
+        <v>3.898553194864228</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.383612720190072</v>
+        <v>1.37318308449192</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>113</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.692324603073004</v>
+        <v>-4.679802313397381</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.525655460061515</v>
+        <v>2.538565269637566</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.401119738336206</v>
+        <v>-1.388112606918604</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.154020356515623</v>
+        <v>-2.141041214117159</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.984704069649716</v>
+        <v>-7.971593265274777</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.041201734038012</v>
+        <v>-5.028158837743646</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.006963668056564</v>
+        <v>-5.993897413756088</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.59172152202234</v>
+        <v>-5.575970177254128</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.888285962750302</v>
+        <v>-3.873206331433394</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.389497588972418</v>
+        <v>-7.372291890568938</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.481582868590593</v>
+        <v>-8.463568575038082</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-9.336087304335166</v>
+        <v>-9.317390568150458</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.45188436916991</v>
+        <v>-4.435472888385455</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-12.16676480680513</v>
+        <v>-12.17719444250329</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.015508042253856</v>
+        <v>4.028030331929479</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.40972263250265</v>
+        <v>2.422632442078701</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5678318616980818</v>
+        <v>0.5808389931156839</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.914244704980767</v>
+        <v>-2.901265562582303</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5607119761303778</v>
+        <v>-0.5476011717554385</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.431632558521791</v>
+        <v>-2.418589662227426</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.681673910872249</v>
+        <v>-4.668607656571773</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-6.594027687059288</v>
+        <v>-6.577392511621305</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.657977934547638</v>
+        <v>-6.641158208783686</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.233049934793797</v>
+        <v>-8.214878878923045</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.270329707383837</v>
+        <v>-6.252889001258005</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-11.30943098683347</v>
+        <v>-11.28896559473655</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-13.18601288013551</v>
+        <v>-13.16451756796122</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.863827779743445</v>
+        <v>-7.874257415441598</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>107</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.020049810039318</v>
+        <v>-2.007527520363695</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.419191898563852</v>
+        <v>-6.406282088987801</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.953666383814472</v>
+        <v>-4.94065925239687</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.960637385377851</v>
+        <v>-2.947658242979387</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.496676955967082</v>
+        <v>-3.483566151592143</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.456605425790549</v>
+        <v>1.469648322084915</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.41991044574258</v>
+        <v>-1.406844191442104</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.816603603445124</v>
+        <v>-2.801636699708254</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.87881334633888</v>
+        <v>-2.863640558399609</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.795394694027905</v>
+        <v>-2.779656688201285</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2013658328335381</v>
+        <v>-0.186828791378737</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7664687074369851</v>
+        <v>0.781025548839466</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.3450720446912072</v>
+        <v>0.3599543632597033</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3397860622844178</v>
+        <v>-0.3502156979825699</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>112</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.5952226721638</v>
+        <v>-1.582700382488177</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.419499099576008</v>
+        <v>-1.406589289999957</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.03828066537393227</v>
+        <v>-0.02527353395633014</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.870758322509879</v>
+        <v>1.883737464908343</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.333765741263036</v>
+        <v>-1.320654936888097</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.928207852241968</v>
+        <v>-1.915164955947603</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.327983051584617</v>
+        <v>3.341049305885093</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1961653701565993</v>
+        <v>0.2095385607684861</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7550553567841618</v>
+        <v>-0.740911426059867</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.744001787057428</v>
+        <v>3.75607059254267</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.216339893921571</v>
+        <v>6.227112476807193</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.79236387001049</v>
+        <v>1.806442955090695</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.26429767887084</v>
+        <v>2.278186843768736</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.514019011146829</v>
+        <v>2.503589375448676</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>127</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.261305533763931</v>
+        <v>0.2738278234395537</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.909956433268285</v>
+        <v>-2.897046623692233</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.52462054618929</v>
+        <v>-2.511613414771688</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.395328524626272</v>
+        <v>-2.382349382227808</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2072519669360204</v>
+        <v>0.2203627713109597</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.203444766644367</v>
+        <v>-4.190401870350001</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.717197075077479</v>
+        <v>-2.704130820777003</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.535479980999703</v>
+        <v>-5.518300745140159</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8876205513012394</v>
+        <v>-0.8732403212841646</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.978612800568179</v>
+        <v>2.99097580657314</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.156628361969553</v>
+        <v>-1.141412662009003</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4505561133545939</v>
+        <v>0.4656204111737878</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.02863963612579568</v>
+        <v>0.04405905441135616</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.296442181204128</v>
+        <v>-1.30687181690228</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>130</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5871890257909129</v>
+        <v>-0.5746667361152902</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.8566384348897174</v>
+        <v>0.8695482444657685</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.431536332437076</v>
+        <v>-6.418529201019474</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.066671223924253</v>
+        <v>-7.053692081525789</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.243097297997586</v>
+        <v>-2.229986493622647</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.243958918734087</v>
+        <v>-4.230916022439722</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.330832122174506</v>
+        <v>-4.31776586787403</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.372896851252769</v>
+        <v>-4.792055277478354</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.136824499529034</v>
+        <v>-2.121324696944043</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.522292225445547</v>
+        <v>-4.504710547172905</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.194185503433147</v>
+        <v>-3.17717235397938</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.39383621071854</v>
+        <v>-2.376417376293546</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.587350672777809</v>
+        <v>-3.568970389057611</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.799167802039989</v>
+        <v>-1.809597437738141</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>174</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.24025141584567</v>
+        <v>3.252773705521292</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.783766761218793</v>
+        <v>2.796676570794844</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.76486969020042</v>
+        <v>-2.751862558782818</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.370897576077432</v>
+        <v>1.383876718475896</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.833962306045521</v>
+        <v>0.8470731104204603</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.131107054753159</v>
+        <v>1.144149951047524</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6682801650382046</v>
+        <v>-0.6552139107377286</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.023653583147834</v>
+        <v>4.036834592443071</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.245466133582688</v>
+        <v>2.257929854312728</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.8257615214509713</v>
+        <v>0.8399781977776897</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.04719947330958263</v>
+        <v>0.06242863859272063</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4934228688071585</v>
+        <v>-0.4765780702892997</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2322779744370465</v>
+        <v>0.2487119715671895</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.09271333696483453</v>
+        <v>-0.1031429726629867</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>161</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9160740398765981</v>
+        <v>0.9285963295522208</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.682569308746011</v>
+        <v>-0.6696594991699598</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.72238722141433</v>
+        <v>5.735394352831932</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.848722092100218</v>
+        <v>5.861701234498682</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.166757799831721</v>
+        <v>7.179868604206661</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.609310119512358</v>
+        <v>5.622353015806723</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.001550212811118</v>
+        <v>8.014616467111594</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.159585616102852</v>
+        <v>8.17276662539809</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.630108426256456</v>
+        <v>5.639120746418179</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.407679020584247</v>
+        <v>5.417794794252949</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.447258046412145</v>
+        <v>6.456957229222809</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.07154135398301</v>
+        <v>12.07749151623721</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.795353579491668</v>
+        <v>9.803582460119785</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.802838886923226</v>
+        <v>8.792409251225074</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>178</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.627177913517563</v>
+        <v>-3.614655623841941</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2242994473382538</v>
+        <v>-0.2113896377622027</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.41038210506602</v>
+        <v>-3.397374973648418</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.512215312191429</v>
+        <v>-5.499236169792965</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6662683192830485</v>
+        <v>0.6793791236579878</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.396954219204737</v>
+        <v>-2.383911322910372</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.046714355689019</v>
+        <v>-3.033648101388543</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1672429468245724</v>
+        <v>-0.1540619375293346</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.597441583493051</v>
+        <v>-1.897588385083949</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3466645734668816</v>
+        <v>0.3616721334168886</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4235257798175027</v>
+        <v>-0.4070299843219516</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.184009427799616</v>
+        <v>1.864664034109623</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.571681306478894</v>
+        <v>4.583838650431893</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.697807133137196</v>
+        <v>3.687377497439044</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.797181343983226</v>
+        <v>4.809703633658849</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.639507367957258</v>
+        <v>4.652417177533309</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.300558756886943</v>
+        <v>2.313565888304545</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.9449680076549</v>
+        <v>-1.931988865256436</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.967595738484206</v>
+        <v>-2.954484934109267</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2401605943152987</v>
+        <v>-0.2271176980209333</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.2992810948802</v>
+        <v>-1.286214840579724</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.768811324717376</v>
+        <v>-1.755630315422138</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1140553452962862</v>
+        <v>0.1272540842510494</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7184836938950667</v>
+        <v>0.7337951041930779</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.9954973394466435</v>
+        <v>1.011553067010126</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.489930959365694</v>
+        <v>2.503383248085804</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.057720760345724</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.122032948429052</v>
+        <v>2.1116033127309</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>221</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-6.318257088848988</v>
+        <v>-6.305734799173365</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-5.663384073172253</v>
+        <v>-5.650474263596202</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.807327290244565</v>
+        <v>-3.794320158826963</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.224594630471444</v>
+        <v>-3.211615488072979</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.922274550076665</v>
+        <v>-6.909163745701726</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.721898054436359</v>
+        <v>-5.708855158141994</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.99806332731729</v>
+        <v>-3.984997073016814</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.106458480331064</v>
+        <v>-3.093277471035826</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.01224865479342441</v>
+        <v>0.0009500841613387934</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.394395911121691</v>
+        <v>1.40937993084632</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.902593179011703</v>
+        <v>3.913949402509402</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3170668340946889</v>
+        <v>0.330519122814799</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.8017895987153949</v>
+        <v>0.8153456450669978</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.051510930991718</v>
+        <v>1.041081295293566</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>185</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.347678967308809</v>
+        <v>2.360201256984432</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.03825558057612</v>
+        <v>5.051165390152171</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2002981628424436</v>
+        <v>-0.1872910314248415</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.698444816602873</v>
+        <v>3.711423959001337</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.006894288972326</v>
+        <v>1.020005093347265</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2270868372612611</v>
+        <v>0.2401297335556265</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1402989205463712</v>
+        <v>0.1533651748468472</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.824190634880672</v>
+        <v>1.83737164417591</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.841467237846416</v>
+        <v>2.854665976801179</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.068060305060584</v>
+        <v>3.080284737029224</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.343219325520209</v>
+        <v>5.038926436615384</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.080305185568335</v>
+        <v>8.093757474288445</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.497888412461272</v>
+        <v>5.511444458812875</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.828690825818605</v>
+        <v>6.818261190120452</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>175</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.573600114657502</v>
+        <v>-5.561077824981879</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.631395459557766</v>
+        <v>-2.618485649981714</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.323193748798218</v>
+        <v>-1.310186617380616</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.6512969316898847</v>
+        <v>-0.6383177892914205</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.180525280426338</v>
+        <v>-1.167414476051398</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2599576574731799</v>
+        <v>0.2730005537675453</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.590557641248886</v>
+        <v>3.603623895549362</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.141759975138839</v>
+        <v>3.154940984434077</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.488555639609224</v>
+        <v>2.501754378563987</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.783493885359015</v>
+        <v>2.790280149250123</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.578740561041435</v>
+        <v>2.592197854751653</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.327409432672589</v>
+        <v>4.340861721392699</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.192869107441965</v>
+        <v>6.206425153793568</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.299733296861106</v>
+        <v>5.289303661162954</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,105 +2210,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 2.982</t>
+          <t>X &gt; 2.983</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2135065962402081</v>
+        <v>-0.2137292923578542</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.0169392863379656</v>
+        <v>0.01665183885000232</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.096367587806931</v>
+        <v>-0.09662960591419534</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.05044741931559571</v>
+        <v>-0.05072008957578333</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.03863207590890738</v>
+        <v>-0.03891058745547582</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.02076303451983108</v>
+        <v>-0.0210444837831929</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.02993422348261987</v>
+        <v>0.0296398150083661</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08906378872780607</v>
+        <v>0.08875234681686806</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2125866456897256</v>
+        <v>0.2122445662682253</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1580225824683552</v>
+        <v>0.1576892123068134</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.138121781141308</v>
+        <v>0.1377920455071404</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.161848831904166</v>
+        <v>0.1615133259602075</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1955941886703556</v>
+        <v>0.1952480668218612</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2635297743562219</v>
+        <v>0.2636948850039289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 6.291</t>
+          <t>X &gt; 6.292</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3998</v>
+        <v>3999</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.36180032469764</v>
+        <v>-0.3622719627377364</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.04017402793732572</v>
+        <v>-0.04074336019753133</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.09728647663786916</v>
+        <v>-0.0978460769317735</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.10316044129506</v>
+        <v>-0.1037174593021533</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1456073795863233</v>
+        <v>0.1449822418200952</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.207166555470188</v>
+        <v>0.2065289493088471</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2110265394063902</v>
+        <v>0.2103867609956325</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2320814940317817</v>
+        <v>0.2314311411810479</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2848449367014894</v>
+        <v>0.2841804467043474</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2481901086759279</v>
+        <v>0.2475253289891484</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2574637373902036</v>
+        <v>0.2567941280435804</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4059808612440108</v>
+        <v>0.4052741897041869</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3999923168157409</v>
+        <v>0.3992822966507106</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4638868021852005</v>
+        <v>0.4642402524536351</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3889</v>
+        <v>3890</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.494463435535458</v>
+        <v>-0.4952639680183424</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.09322008493019496</v>
+        <v>-0.09415235424913249</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2178293577195447</v>
+        <v>-0.2187371330648276</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2018921904154354</v>
+        <v>-0.2028022109187049</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1363709387567837</v>
+        <v>-0.1373077562806557</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.02116124216736637</v>
+        <v>0.02018880546360435</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1044541593988626</v>
+        <v>0.1034583673402807</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1391449055881324</v>
+        <v>0.138131441370497</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01530518088661381</v>
+        <v>0.01432193551079308</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.05273171149383415</v>
+        <v>0.05172328478527533</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.04225546340525455</v>
+        <v>0.04124559611894085</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1682142202776831</v>
+        <v>0.1671721016599079</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1994794636667194</v>
+        <v>0.1984213354582209</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1809734246941943</v>
+        <v>0.181701751504491</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6366743944805293</v>
+        <v>-0.6379035669968331</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1649747880428976</v>
+        <v>-0.1663726806273544</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3066746949725143</v>
+        <v>-0.308046233213922</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3744058453634835</v>
+        <v>-0.3757566450196279</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4205288072062885</v>
+        <v>-0.4218824360447826</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2148564525145176</v>
+        <v>-0.2162574623093789</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03367118789970647</v>
+        <v>0.03220118411526585</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.006224438517541842</v>
+        <v>0.004748500857658655</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.09327391966393606</v>
+        <v>-0.09472579188830821</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07790315949986848</v>
+        <v>-0.07938260011186316</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.001806551420571623</v>
+        <v>-0.003312457855180639</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.20716468672952</v>
+        <v>0.2056033627300806</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.227690060836629</v>
+        <v>0.2261112405187617</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2263845003289262</v>
+        <v>0.2274926674733067</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3628</v>
+        <v>3629</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6802515070231578</v>
+        <v>-0.6819596998559732</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2990212764003957</v>
+        <v>-0.3008933323893928</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4317113159665382</v>
+        <v>-0.4335621590814398</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6715246751589206</v>
+        <v>-0.6733058688880078</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.5901169290561725</v>
+        <v>-0.59194094233127</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2376694907904593</v>
+        <v>-0.2246265944960939</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.02267875542935371</v>
+        <v>0.02069604953807413</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06587455842473844</v>
+        <v>0.0638620605785718</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.02007654354962085</v>
+        <v>0.01807341119720007</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.03868582997827019</v>
+        <v>0.03664577877017194</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.04217054884487226</v>
+        <v>0.04012107690395084</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2298100623459476</v>
+        <v>0.2277091070007558</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2935658755402244</v>
+        <v>0.2914310569812955</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.283352764493813</v>
+        <v>0.2848553676543233</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7240319275159166</v>
+        <v>-0.7115096378402939</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3796336859575646</v>
+        <v>-0.3820564614977258</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5021650486800198</v>
+        <v>-0.5045726233974719</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6135578127902903</v>
+        <v>-0.6159287759584586</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5080487222354861</v>
+        <v>-0.5104763354555217</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2677496416626823</v>
+        <v>-0.2547067453683169</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1774803041524464</v>
+        <v>0.1748686096512273</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.183388049111926</v>
+        <v>0.1807514213823893</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.0524270282283652</v>
+        <v>0.04982360857392365</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1048407307333221</v>
+        <v>0.1021810915281307</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.0592228827254786</v>
+        <v>0.05656529509163732</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3673145761839081</v>
+        <v>0.3645690584047543</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3068112774963652</v>
+        <v>0.3040619188602207</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.2578416261034633</v>
+        <v>0.2598161146413389</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8336872828655686</v>
+        <v>-0.8211649931899458</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.324994144855232</v>
+        <v>-0.3280238781921341</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5123324630735269</v>
+        <v>-0.4993253316559247</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6626286934029437</v>
+        <v>-0.6655721714651222</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3841685679785911</v>
+        <v>-0.3872273603279339</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05706184236616707</v>
+        <v>-0.04401894607180168</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1117811599289595</v>
+        <v>0.1085889978361578</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.01262778896779082</v>
+        <v>-0.01581173400833791</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.05725300290792745</v>
+        <v>-0.06042893619532919</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1485072503723899</v>
+        <v>0.1452193387668572</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2278365630786183</v>
+        <v>0.2245114870652927</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3978827928933413</v>
+        <v>0.3945074220972131</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4106370707509512</v>
+        <v>0.4072317765912743</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2907702111808135</v>
+        <v>0.2932105747012628</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.028745134887743</v>
+        <v>-1.01622284521212</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1568317974555384</v>
+        <v>-0.1605572577332381</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3049392455697131</v>
+        <v>-0.291932114152111</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3739471615909693</v>
+        <v>-0.3776230717358686</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1549623024824101</v>
+        <v>-0.1587453846917839</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1044339450136604</v>
+        <v>-0.09139104871929504</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.07465023608994414</v>
+        <v>0.07081217226144787</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.0258639931879685</v>
+        <v>0.02200629056788017</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.07987225756222216</v>
+        <v>-0.0837036765843493</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1686254410715335</v>
+        <v>0.1646557542625686</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2594647827239243</v>
+        <v>0.2554505476706055</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4968590306936065</v>
+        <v>0.4927716352809668</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5581203115425453</v>
+        <v>0.5539823584936272</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3923782756447025</v>
+        <v>0.3953086985011254</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.279453211760639</v>
+        <v>-1.266930922085017</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2513849901690506</v>
+        <v>-0.2559091808982785</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6462536967656405</v>
+        <v>-0.6332465653480384</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.725312638358659</v>
+        <v>-0.7297053595835123</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3567043749727858</v>
+        <v>-0.3435935705978466</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2212319869817705</v>
+        <v>-0.2081890906874051</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.09391470788413159</v>
+        <v>-0.09853599028398463</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1544201728588561</v>
+        <v>-0.1590642133781799</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2624342925924807</v>
+        <v>-0.2670511418043873</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1378333506293927</v>
+        <v>0.1330116681906546</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2108903709978733</v>
+        <v>0.2060248321855127</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5232642108058343</v>
+        <v>0.5182975237473784</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6733885879614547</v>
+        <v>0.668334552411828</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3571266991716939</v>
+        <v>0.3607322325915305</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.218361815619694</v>
+        <v>-1.205839525944072</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1934473073238934</v>
+        <v>-0.1988685295825405</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7923976465735478</v>
+        <v>-0.7793905151559457</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9500970546284435</v>
+        <v>-0.95528782054717</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.467762910734983</v>
+        <v>-0.4546521063600437</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4425224020768255</v>
+        <v>-0.4294795057824601</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4067087795320745</v>
+        <v>-0.4121143291520681</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3446825658783368</v>
+        <v>-0.3501597735111801</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3529515796714477</v>
+        <v>-0.3584353644507985</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.144408949851595</v>
+        <v>0.1386662376128598</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.06106600655706984</v>
+        <v>0.05532757001083866</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.489700602123655</v>
+        <v>0.4838162447153209</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7368176554832928</v>
+        <v>0.7308029239947302</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4602343447726014</v>
+        <v>0.4645131719795614</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8679966240969037</v>
+        <v>-0.855474334421281</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.09299355212085914</v>
+        <v>-0.09916926140736848</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8413440544049635</v>
+        <v>-0.8283369229873614</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.010363009284966</v>
+        <v>-1.016245395517778</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5586852144561476</v>
+        <v>-0.5455744100812083</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4734073502906995</v>
+        <v>-0.4603644539963341</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.43287145333084</v>
+        <v>-0.4389927764873889</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3500681327038251</v>
+        <v>-0.356276035954707</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3562671495877723</v>
+        <v>-0.36248357575586</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1586456457798988</v>
+        <v>0.1521455363999635</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1155048948302166</v>
+        <v>0.1089926746626162</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4179227464318203</v>
+        <v>0.4113035006548813</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7267223509726293</v>
+        <v>0.7199414036670078</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4294192137810668</v>
+        <v>0.4342877093728106</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7834011454887815</v>
+        <v>-0.7708788558131587</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.05296732350880262</v>
+        <v>-0.04005751393275148</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9682821267596751</v>
+        <v>-0.9552749953420729</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.301572468115353</v>
+        <v>-1.308321227218386</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7987143972076041</v>
+        <v>-0.7856035928326648</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7987808269147791</v>
+        <v>-0.7857379306204137</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6402809779825844</v>
+        <v>-0.647317014319448</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.5663199556536256</v>
+        <v>-0.5734500341355115</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5325334665772132</v>
+        <v>-0.5396886503318541</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.09022439879343835</v>
+        <v>0.08271967038871963</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.01816998407741721</v>
+        <v>0.010660211761504</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.371709523189601</v>
+        <v>0.3640680232875226</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9792758401574204</v>
+        <v>0.9713471494274586</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3926090894758048</v>
+        <v>0.3982841661166248</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2554</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6777413268480075</v>
+        <v>-0.6652190371723847</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.01447264316313834</v>
+        <v>0.02738245273918949</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.005152018138652</v>
+        <v>-0.9921448867210501</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.109182368545596</v>
+        <v>-1.096203226147132</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7495168987290555</v>
+        <v>-0.7364060943541162</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6863584440278316</v>
+        <v>-0.6733155477334662</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4375280017921099</v>
+        <v>-0.4456479296470377</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3364199537193642</v>
+        <v>-0.3446553912783656</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2587075240506707</v>
+        <v>-0.2669878066913327</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3987796555137706</v>
+        <v>0.3901079932419407</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.568233071660714</v>
+        <v>0.5594585955751654</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7814211743555575</v>
+        <v>0.7725630404179498</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.127425545522286</v>
+        <v>1.118362531484372</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8681413962010822</v>
+        <v>0.8577117605029301</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2440</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4296867877212094</v>
+        <v>-0.4171644980455866</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.042924315293277</v>
+        <v>0.05583412486932815</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9649398960029458</v>
+        <v>-0.9519327645853437</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.9164194973553919</v>
+        <v>-0.9034403549569276</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6783797398080296</v>
+        <v>-0.6652689354330903</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7078687379321664</v>
+        <v>-0.694825841637801</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4843838378509844</v>
+        <v>-0.4934716320441481</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2749983382014278</v>
+        <v>-0.2842570368221189</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.354456683646255</v>
+        <v>-0.3636992809299784</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3324091534719926</v>
+        <v>0.3227348792732414</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5193045016053759</v>
+        <v>0.509512631665288</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6998563221207021</v>
+        <v>0.6899900705210413</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.204578709315506</v>
+        <v>1.194427728850634</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.167414795690149</v>
+        <v>1.156985159991997</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2330</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5892876997564045</v>
+        <v>-0.5767654100807817</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3237428806897</v>
+        <v>0.3366526902657512</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.8413440544049635</v>
+        <v>-0.8283369229873614</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.138989937629731</v>
+        <v>-1.126010795231267</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.9071929242038266</v>
+        <v>-0.8940821198288873</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8237004944042994</v>
+        <v>-0.810657598109934</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.971025433298955</v>
+        <v>-0.9809477605425627</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3445367485393476</v>
+        <v>-0.3548223433331685</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2106703163188968</v>
+        <v>-0.2210316859167776</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1629562575346313</v>
+        <v>0.1522668670943546</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5397795220804014</v>
+        <v>0.5288826872787524</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6843377896009386</v>
+        <v>0.6733782614564063</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.189803503517993</v>
+        <v>1.17854012590854</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.224932561116162</v>
+        <v>1.21450292541801</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4250929964689689</v>
+        <v>-0.4125707067933462</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3014628869696452</v>
+        <v>0.3143726965456963</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9477223663895344</v>
+        <v>-0.9347152349719323</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.267109521551816</v>
+        <v>-1.254130379153352</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.131070304969306</v>
+        <v>-1.117959500594367</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.148376568692498</v>
+        <v>-1.135333672398133</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9183620845259242</v>
+        <v>-0.9052958302254481</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2817321776766306</v>
+        <v>-0.2932277833646992</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1380152359008235</v>
+        <v>-0.1495963028618803</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3423798440648795</v>
+        <v>0.330395219775383</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7035796858805554</v>
+        <v>0.6913809768974133</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9889686936009312</v>
+        <v>0.976640357171334</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.406059884203522</v>
+        <v>1.393446334505612</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.295095914405877</v>
+        <v>1.284666278707725</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>2109</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.200294112172152</v>
+        <v>-0.1877718224965292</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3630731732087469</v>
+        <v>0.375982982784798</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9301406870521447</v>
+        <v>-0.9171335556345426</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.083575497707059</v>
+        <v>-1.070596355308595</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.101902150131473</v>
+        <v>-1.088791345756533</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.088148155678226</v>
+        <v>-1.075105259383861</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.747349958056887</v>
+        <v>-0.7342837037564109</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2902438627306623</v>
+        <v>-0.303007193878841</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.006007685085073433</v>
+        <v>-0.006919182143633407</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3183964827616208</v>
+        <v>0.3051134677478444</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7088075570487504</v>
+        <v>0.6952822703360724</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.196739155082881</v>
+        <v>1.182981231442092</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.277878929293898</v>
+        <v>1.263974239778676</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.290521077122577</v>
+        <v>1.280091441424425</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1996</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.05401422724256832</v>
+        <v>0.06653651691819107</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2406424124801134</v>
+        <v>0.2535522220561646</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.903477043367225</v>
+        <v>-0.8904699119496229</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.022974160509975</v>
+        <v>-1.00999501811151</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.7122445264312915</v>
+        <v>-0.6991337220563523</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8643530382660813</v>
+        <v>-0.851310141971716</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4495862560378683</v>
+        <v>-0.4365200017373922</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.009889892529834299</v>
+        <v>-0.004487746423230021</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2264762132440907</v>
+        <v>0.2119638077710633</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.7547652353197094</v>
+        <v>0.7397561558689887</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.229105211406086</v>
+        <v>1.213794367293637</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.793036444619077</v>
+        <v>1.777441157972127</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.602259316431372</v>
+        <v>1.586638330701795</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.052381450310868</v>
+        <v>2.041951814612716</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1858</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2402194360898093</v>
+        <v>-0.2276971464141866</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.07953742304894718</v>
+        <v>0.09244723262499832</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.012756176251514</v>
+        <v>-0.9997490448339121</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8825030436440144</v>
+        <v>-0.8695239012455502</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7234993660123124</v>
+        <v>-0.7103885616373731</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7479458403138253</v>
+        <v>-0.7349029440194599</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1352546648822468</v>
+        <v>-0.1221884105817708</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5003853855240834</v>
+        <v>0.4837043190220527</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7378081144256114</v>
+        <v>0.7209685646518906</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.422320936867429</v>
+        <v>1.404847455546751</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.786113832930845</v>
+        <v>1.768370419425025</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.766201409926104</v>
+        <v>2.747927773620042</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.700634754066598</v>
+        <v>2.682257014240818</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.788892146622757</v>
+        <v>2.778462510924605</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1751</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1314576713767366</v>
+        <v>-0.1189353817011138</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4766613735986738</v>
+        <v>0.4895711831747249</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7719352783593223</v>
+        <v>-0.7589281469417202</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.7555125384666752</v>
+        <v>-0.742533396068211</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5540362008922912</v>
+        <v>-0.5409253965173519</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8826614231083312</v>
+        <v>-0.8696185268139658</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.05675199866177394</v>
+        <v>-0.04368574436129791</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7030797440733139</v>
+        <v>0.6844647353579418</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9588123955802672</v>
+        <v>0.9400166378480606</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.680056843495528</v>
+        <v>1.660553876666711</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.907564617760535</v>
+        <v>1.88784861220401</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.888400952568212</v>
+        <v>2.868121113455281</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.844578334822245</v>
+        <v>2.824168141399575</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.980079221638789</v>
+        <v>2.969649585940637</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1639</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.03143224118262111</v>
+        <v>-0.01890995150699837</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6062342674336705</v>
+        <v>0.6191440770097216</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.822069089618843</v>
+        <v>-0.8090619582012408</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9349770512362738</v>
+        <v>-0.9219979088378096</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5007538894087418</v>
+        <v>-0.4876430850338025</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8112146872553865</v>
+        <v>-0.7981717909610211</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2880456689653599</v>
+        <v>-0.2749794146648838</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.7377194084288163</v>
+        <v>0.7169185068979118</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.075928434790043</v>
+        <v>1.054881764850919</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.539018506900689</v>
+        <v>1.517358103525709</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.613127259047886</v>
+        <v>1.591327835611231</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.96329793441474</v>
+        <v>2.940670200543039</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.884231436388184</v>
+        <v>2.861477418601929</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.011927143283145</v>
+        <v>3.001497507584993</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1512</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.05602066540101447</v>
+        <v>-0.04349837572539172</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9015756821090335</v>
+        <v>0.9144854916850846</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6790637754756901</v>
+        <v>-0.666056644058088</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8123152541988929</v>
+        <v>-0.7993361118004287</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5602226352789756</v>
+        <v>-0.5471118309040364</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5262853088940105</v>
+        <v>-0.5132424125996451</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.08400980350489107</v>
+        <v>-0.07094354920441504</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.264634965609645</v>
+        <v>1.240643933491064</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.240856160473633</v>
+        <v>1.216833818382106</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.418100203133655</v>
+        <v>1.39358201338878</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.845772076421703</v>
+        <v>1.820863578466891</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.174354952453527</v>
+        <v>3.148561287348528</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.124086038658902</v>
+        <v>3.098125654218464</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.373807370935189</v>
+        <v>3.363377735237037</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1382</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.006055479546674292</v>
+        <v>0.006466810128948453</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.9058027748286506</v>
+        <v>0.9187125844047017</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1379484119409753</v>
+        <v>-0.1249412805233732</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.223989439391147</v>
+        <v>-0.2110102969926828</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4019203877005282</v>
+        <v>-0.3888095833255889</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1765765033374223</v>
+        <v>-0.1635336070430569</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3154742062107729</v>
+        <v>0.328540460511249</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.794938247948373</v>
+        <v>1.808119257243611</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.558582995350868</v>
+        <v>1.530842940663163</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.976892544461649</v>
+        <v>1.948414164527001</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.31986359985234</v>
+        <v>2.291011676309161</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.698135597324999</v>
+        <v>3.668277080599957</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.755407871138473</v>
+        <v>3.725276512124317</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.860411403125326</v>
+        <v>3.849981767427174</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>1208</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.473652664810146</v>
+        <v>-0.4611303751345233</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.6353013397029272</v>
+        <v>0.6482111492789784</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2404326331063373</v>
+        <v>0.2534397645239395</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.453716542612618</v>
+        <v>-0.4407374002141538</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5799366035215598</v>
+        <v>-0.5668257991466206</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3649348966385446</v>
+        <v>-0.3518920003441792</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4571739252482914</v>
+        <v>0.4702401795487674</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.473914681454417</v>
+        <v>1.487095690749655</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.459644530075764</v>
+        <v>1.426113534226879</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.14270115208074</v>
+        <v>2.108072987552156</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.647217538609326</v>
+        <v>2.612016186708715</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.301886568440047</v>
+        <v>4.26530091855917</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.262878568179907</v>
+        <v>4.226039947601912</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.429818443502555</v>
+        <v>4.419388807804403</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>1047</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6873546700198574</v>
+        <v>-0.6748323803442347</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.8379538462934448</v>
+        <v>0.850863655869496</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6025422367289934</v>
+        <v>-0.5895351053113913</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.422859446326818</v>
+        <v>-1.409880303928354</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.771166592957925</v>
+        <v>-1.758055788582986</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.283610586801196</v>
+        <v>-1.27056769050683</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7029450645297572</v>
+        <v>-0.6898788102292812</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.4458411184377979</v>
+        <v>0.4590221277330357</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.8183411038244799</v>
+        <v>0.7782681080923908</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.640636742501876</v>
+        <v>1.599128182510292</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.062875110952916</v>
+        <v>2.020769283323084</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.107125899411955</v>
+        <v>3.063999403538951</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.412135037309618</v>
+        <v>3.368366266116361</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.757367353349039</v>
+        <v>3.746937717650887</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>869</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.08518143947602397</v>
+        <v>-0.07265914980040122</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.055538525541365</v>
+        <v>1.068448335117417</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.02740357555064321</v>
+        <v>-0.01439644413304109</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.585223837438555</v>
+        <v>-0.5722446950400908</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.270434043336408</v>
+        <v>-2.257323238961469</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.055560912960196</v>
+        <v>-1.042518016665831</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2228634375719309</v>
+        <v>-0.2097971832714549</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.5714210535548361</v>
+        <v>0.5846020628500739</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.313173460950516</v>
+        <v>1.326372199905279</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.905685126953237</v>
+        <v>1.852600192566243</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.572172416542259</v>
+        <v>2.518063034348181</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.296210746301483</v>
+        <v>3.309663035021593</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.174621532232365</v>
+        <v>3.119397239179456</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.76956726036596</v>
+        <v>3.759137624667808</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>664</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.592537419309075</v>
+        <v>-1.580015129633452</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.05095787912017613</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7461268860170662</v>
+        <v>-0.7331197545994641</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1654233029591126</v>
+        <v>-0.1524441605606484</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.055195869382644</v>
+        <v>-2.042085065007704</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.307303481216522</v>
+        <v>-1.294260584922156</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1094643030127003</v>
+        <v>0.1225305573131763</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.293932555882847</v>
+        <v>1.307113565178085</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.683383120150992</v>
+        <v>1.696581859105756</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.272215689870293</v>
+        <v>2.198014414127243</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.058947101488947</v>
+        <v>2.983175298360685</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.545137487750033</v>
+        <v>3.558589776470143</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.124882876805131</v>
+        <v>3.138438923156734</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.27821866691275</v>
+        <v>4.267789031214598</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>443</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.7649886460821662</v>
+        <v>0.777510935757789</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.748920651095432</v>
+        <v>2.761830460671483</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.7810182366336704</v>
+        <v>0.7940253680512726</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.360709571488357</v>
+        <v>1.373688713886821</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3728501541690008</v>
+        <v>0.3859609585439401</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8950111930082585</v>
+        <v>0.9080540893026239</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.158592082477554</v>
+        <v>2.17165833677803</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.489161492684815</v>
+        <v>3.502342501980053</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.529285202008133</v>
+        <v>2.542483940962896</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.710134811999943</v>
+        <v>2.591441549127417</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.638076259203324</v>
+        <v>2.518838781392581</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.155529393975385</v>
+        <v>5.168981682695495</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.283807514407464</v>
+        <v>4.297363560759067</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.887930652552818</v>
+        <v>5.877501016854666</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>258</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.369886196657859</v>
+        <v>-0.3573639069822363</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.107343279180981</v>
+        <v>1.120253088757032</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.48467534478516</v>
+        <v>1.497682476202762</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3155734531092662</v>
+        <v>-0.302594310710802</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08179389598066678</v>
+        <v>-0.0686830916057275</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.373949200036151</v>
+        <v>1.386992096330516</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.605817799366186</v>
+        <v>3.618884053666662</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.683035944986237</v>
+        <v>4.696216954281475</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.305433742201615</v>
+        <v>2.318632481156378</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.453482811161898</v>
+        <v>2.240914457027287</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6983418899450911</v>
+        <v>0.7117991836553088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.058306442639363</v>
+        <v>3.071758731359473</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.413245630144068</v>
+        <v>3.426801676495671</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.213354559319583</v>
+        <v>5.202924923621431</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>10.60179977502812</v>
+        <v>10.61432206470374</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>8.990226162063863</v>
+        <v>9.003135971639914</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3922772547414439</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.932714194664484</v>
+        <v>7.945895203959722</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.757676329420974</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.266354103330329</v>
+        <v>-3.252896809620111</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3824868853404055</v>
+        <v>0.3959391740605156</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.447406279821372</v>
+        <v>-2.433850233469769</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>5.031230715105515</v>
+        <v>5.020801079407363</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,105 +3904,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 2.982</t>
+          <t>X &lt; 2.983</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.833452693562514</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.257040450588846</v>
+        <v>1.270106704889322</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.413999977232102</v>
+        <v>-6.400801238277339</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.679291463178622</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.706973724672849</v>
+        <v>-2.693516430962632</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.863066757803601</v>
+        <v>-3.849614469083491</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.4737975592247</v>
+        <v>-5.460241512873097</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.805934434075141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 6.291</t>
+          <t>X &lt; 6.292</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>174</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.851389265996922</v>
+        <v>7.863911555672544</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.642114503607381</v>
+        <v>1.655024313183432</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.821958440688945</v>
+        <v>1.834965572106547</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.526924216974614</v>
+        <v>2.539903359373078</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.183910791201008</v>
+        <v>-3.170799986826069</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.035894140841663</v>
+        <v>-4.022851244547297</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.545915214435787</v>
+        <v>-3.532848960135311</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.013098613217288</v>
+        <v>-3.99991760392205</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.648811143077744</v>
+        <v>-4.63561240412298</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.774798397071201</v>
+        <v>-3.76139326941837</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.979551721388781</v>
+        <v>-3.966094427678563</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.39344442611231</v>
+        <v>-7.3799921373922</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-7.238986393379051</v>
+        <v>-7.225430347027448</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.713402992137247</v>
+        <v>-8.723832627835399</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>283</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.517162386503806</v>
+        <v>6.529684676179428</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.725376759405272</v>
+        <v>1.738286568981323</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.743935614646134</v>
+        <v>2.756942746063736</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.874188747253633</v>
+        <v>2.887167889652098</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.982410641722112</v>
+        <v>1.995521446097051</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1597112366815807</v>
+        <v>0.1727541329759461</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6317362615094311</v>
+        <v>-0.618670007208955</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.098919660290932</v>
+        <v>-1.085738650995694</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.9602217962829585</v>
+        <v>0.9734205352377217</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4634535017143975</v>
+        <v>0.4768586293672286</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6120570678561847</v>
+        <v>0.6255143615664025</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.12034422709521</v>
+        <v>-1.106891938375099</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.540598838040111</v>
+        <v>-1.527042791688508</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.290877505763824</v>
+        <v>-1.301307141461976</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>415</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.578850836416535</v>
+        <v>5.591373126092158</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.798602524657099</v>
+        <v>1.81151233423315</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.608553095168936</v>
+        <v>2.621560226586539</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.461697794041491</v>
+        <v>3.474676936439955</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.887132000656081</v>
+        <v>3.90024280503102</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.256863094998245</v>
+        <v>2.26990599129261</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2444185343524623</v>
+        <v>0.2574847886529383</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5001267018360238</v>
+        <v>0.5133077111312616</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.643946092762164</v>
+        <v>1.657144831716927</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.516712473999291</v>
+        <v>1.530117601652123</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8300314388383399</v>
+        <v>0.8434887325485576</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.063296247189719</v>
+        <v>-1.049843958469609</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.242587002712938</v>
+        <v>-1.229030956361335</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.233829525858333</v>
+        <v>-1.244259161556485</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>544</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.387295624744155</v>
+        <v>4.399817914419778</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.225263296183563</v>
+        <v>2.238173105759614</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.747825782247531</v>
+        <v>2.760832913665134</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.529455061644015</v>
+        <v>4.542434204042479</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.991033846571845</v>
+        <v>4.004144650946785</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.82321674489193</v>
+        <v>1.73271134113233</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2678947923255421</v>
+        <v>0.2809610466260182</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.01546507704419753</v>
+        <v>-0.002284067748959728</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4750056250087979</v>
+        <v>0.4882043639635611</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3601745576279214</v>
+        <v>0.3735796852807525</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3392447627221102</v>
+        <v>0.352702056432328</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.9131367858148067</v>
+        <v>-0.8996844970946967</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.333391396759708</v>
+        <v>-1.319835350408106</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.267493593895189</v>
+        <v>-1.277923229593341</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>680</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.600541121787089</v>
+        <v>3.530814174744236</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.135810386943248</v>
+        <v>2.148720196519299</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.475156070948707</v>
+        <v>2.488163202366309</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.192780716037852</v>
+        <v>3.205759858436316</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.654359500965683</v>
+        <v>2.667470305340622</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.565863803715466</v>
+        <v>1.496415553771598</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5776934429685809</v>
+        <v>-0.5646271886681049</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6037003711618496</v>
+        <v>-0.5905193618666118</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2176526838323269</v>
+        <v>0.2308514227870901</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.04423720707795553</v>
+        <v>-0.03083207942512445</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1921859391926972</v>
+        <v>0.205643232902915</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.391077962285394</v>
+        <v>-1.377625673565284</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.076038455583237</v>
+        <v>-1.062482409231635</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.82631712330695</v>
+        <v>-0.8367467590051021</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>809</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.363528387558212</v>
+        <v>3.307261309367128</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.505345650056341</v>
+        <v>1.518255459632393</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.043329236772387</v>
+        <v>1.986616010758986</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.790866319997171</v>
+        <v>2.803845462395635</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.635161154307717</v>
+        <v>1.648271958682656</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3955736851958633</v>
+        <v>0.3407077167128065</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1835976093322884</v>
+        <v>-0.1705313550318124</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3380941463979639</v>
+        <v>0.3512751556932017</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6479224431575545</v>
+        <v>0.6611211821123177</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2022027418703729</v>
+        <v>-0.1887976142175418</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5305654605019114</v>
+        <v>-0.5171081667916937</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.237838669040293</v>
+        <v>-1.224386380320183</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.287265097043289</v>
+        <v>-1.273709050691686</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7903249761390683</v>
+        <v>-0.8007546118372204</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>940</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.451359981276227</v>
+        <v>3.404555867662893</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6720581305200355</v>
+        <v>0.6849679400960866</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.973020529198358</v>
+        <v>0.9271392305002806</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.315813513027962</v>
+        <v>1.328792655426426</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5648524467336884</v>
+        <v>0.5779632511086277</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4957761942035717</v>
+        <v>0.4502575782995066</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.01448943796232527</v>
+        <v>-0.001423183661849237</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1566250355966048</v>
+        <v>0.1698060448918426</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6275400430313169</v>
+        <v>0.6407387819860801</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2225851419966105</v>
+        <v>-0.2091800143437794</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5337214450375853</v>
+        <v>-0.5202641513273676</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.350402117479391</v>
+        <v>-1.33694982875928</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.557890770977487</v>
+        <v>-1.544334724625884</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.9890205025309768</v>
+        <v>-0.999450138229129</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>1093</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.528459490009006</v>
+        <v>3.489913504561358</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.821995366095841</v>
+        <v>0.8349051756718922</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.755827122786251</v>
+        <v>1.71750605369057</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.068728657220241</v>
+        <v>2.081707799618705</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.033450363687727</v>
+        <v>0.9954730410435602</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7416347525341536</v>
+        <v>0.7040814499829366</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4739184186104524</v>
+        <v>0.4869846729109284</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6471741781089122</v>
+        <v>0.66035518740415</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.043630833555156</v>
+        <v>1.056829572509919</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.08096827644990157</v>
+        <v>-0.06756314879707048</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.2857216007674808</v>
+        <v>-0.272264307057263</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.166251526679133</v>
+        <v>-1.152799237959023</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.586506137624035</v>
+        <v>-1.572950091272432</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6963456470677869</v>
+        <v>-0.706775282765939</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>1241</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.812027917732152</v>
+        <v>2.78012814617248</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.5573674880476318</v>
+        <v>0.570277297623683</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.815485410108501</v>
+        <v>1.783222954669291</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.267540634429601</v>
+        <v>2.280519776828065</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.130598620759685</v>
+        <v>1.09862604030517</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.150875890742057</v>
+        <v>1.1190222631433</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.146722350746167</v>
+        <v>1.159788605046643</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.001859661070228</v>
+        <v>1.015040670365465</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.10202012944071</v>
+        <v>1.115218868395473</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.07042576469278572</v>
+        <v>-0.05702063703995464</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1277217973715921</v>
+        <v>0.1411790910818098</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8854373498760566</v>
+        <v>-0.8719850611559465</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.466852315373735</v>
+        <v>-1.453296269022132</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.8142300967154981</v>
+        <v>-0.8246597324136502</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>1352</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.750104115214377</v>
+        <v>1.722623792474501</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2861319782648764</v>
+        <v>0.2990417878409275</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.70395983290274</v>
+        <v>1.675488115263022</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.129633940399451</v>
+        <v>2.142613082797915</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.189512253374268</v>
+        <v>1.161192067368397</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.084659487669519</v>
+        <v>1.056538107339939</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.073890267438664</v>
+        <v>1.08695652173914</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.9025648568228419</v>
+        <v>0.9157458661180797</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9894939647233727</v>
+        <v>1.002692703678136</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.08252471142881035</v>
+        <v>-0.06911958377597927</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.008579952419296433</v>
+        <v>0.02203724612951419</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6227173636080607</v>
+        <v>-0.6092650748879507</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.264865465677225</v>
+        <v>-1.251309419325622</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6453216481938284</v>
+        <v>-0.6557512838919806</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1491</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.329244397273136</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1787899409890841</v>
+        <v>0.155389515197804</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.695698730624358</v>
+        <v>1.671091685756551</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.361785754725496</v>
+        <v>2.37476489712396</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.459243502965577</v>
+        <v>1.43459992540803</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.526214141033492</v>
+        <v>1.501631822230294</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.307342261454039</v>
+        <v>1.320408515754515</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.175504268440477</v>
+        <v>1.188685277735715</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.181573463411759</v>
+        <v>1.194772202366522</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.06317195376948348</v>
+        <v>0.07657708142231456</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1937640352198429</v>
+        <v>0.2072213289300606</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4425436189706033</v>
+        <v>-0.4290913302504933</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.533489041451396</v>
+        <v>-1.519932995099794</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4789387353320436</v>
+        <v>-0.4893683710301957</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.016413896538793</v>
+        <v>0.9960070463887263</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.05395294667788875</v>
+        <v>0.033513639948616</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.542042911400571</v>
+        <v>1.520520206988735</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.768558797586834</v>
+        <v>1.746927467540935</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.203062388875622</v>
+        <v>1.181558072268999</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.16456307341717</v>
+        <v>1.143176852515282</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.8327632659657667</v>
+        <v>0.8458295202662427</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6744124799081703</v>
+        <v>0.6875934892034081</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6134125937258688</v>
+        <v>0.626611332680632</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.4220121589364041</v>
+        <v>-0.408607031283573</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6885320057987627</v>
+        <v>-0.675074712088545</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.024747983722023</v>
+        <v>-1.011295695001913</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.568535639756476</v>
+        <v>-1.554979593404873</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.161153159080961</v>
+        <v>-1.143944375544002</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5560438431962353</v>
+        <v>0.5380603926973961</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.01128052508713751</v>
+        <v>-0.00694677262004717</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.318091710459591</v>
+        <v>1.298964142769407</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.307605922231488</v>
+        <v>1.288512925557718</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9743042189409792</v>
+        <v>0.955206174358473</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.073178558815428</v>
+        <v>1.054108545453893</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8153346280405529</v>
+        <v>0.8284008823410289</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5212614427616487</v>
+        <v>0.5344424520568865</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6910751745828136</v>
+        <v>0.7042739135375768</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2744568194468542</v>
+        <v>-0.2610516917940231</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5369135482652965</v>
+        <v>-0.5234562545550787</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7910474134241952</v>
+        <v>-0.7775951247040851</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.499819046873419</v>
+        <v>-1.486263000521816</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.449194449757165</v>
+        <v>-1.433637563797888</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6992023724307188</v>
+        <v>0.6829563329053485</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.34215324340704</v>
+        <v>-0.3583358898319489</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.025579815267101</v>
+        <v>1.008524434256415</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.45693075841934</v>
+        <v>1.439667994931781</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.16570398926126</v>
+        <v>1.148422515743789</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.113755668003229</v>
+        <v>1.096579278802736</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.35457810916828</v>
+        <v>1.367644363468756</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5618385519494495</v>
+        <v>0.5750195612446873</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4465793060275942</v>
+        <v>0.4597780449823574</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.02373036082344981</v>
+        <v>-0.01032523317061873</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4997804838387978</v>
+        <v>-0.4863231901285801</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.682434765451589</v>
+        <v>-0.6689824767314789</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.31972681535472</v>
+        <v>-1.306170769003117</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.365692482571177</v>
+        <v>-1.351731917474353</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4387391402693694</v>
+        <v>0.4242827462240584</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2784813209293375</v>
+        <v>-0.2930200226292854</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.038659431694214</v>
+        <v>1.023330573279431</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.452640112857104</v>
+        <v>1.43712396805801</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.300433648740494</v>
+        <v>1.284837363038328</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.37098830750471</v>
+        <v>1.355425381064265</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.161436991814028</v>
+        <v>1.145946611404071</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4384991173292079</v>
+        <v>0.4516801266244457</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3263483360062338</v>
+        <v>0.339547074960997</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2168714781777012</v>
+        <v>-0.2034663505248702</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.626228383057942</v>
+        <v>-0.6127710893477243</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9499014916971618</v>
+        <v>-0.9364492029770517</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.421306997782736</v>
+        <v>-1.407750951431133</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.296845150280276</v>
+        <v>-1.284317091485924</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1635665107079021</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3109085015647608</v>
+        <v>-0.3239861815691967</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9159800952388508</v>
+        <v>0.9022033403659648</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.121422323509144</v>
+        <v>1.10756826966454</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.142290096738371</v>
+        <v>1.12828414309736</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.176318154947481</v>
+        <v>1.162358667437658</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.8763649245644771</v>
+        <v>0.8625199413703584</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4091815257829765</v>
+        <v>0.4223625350782143</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1543831899882733</v>
+        <v>0.1675819289430365</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.162796258605546</v>
+        <v>-0.1493911309527149</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5613480325355269</v>
+        <v>-0.5478907388253091</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.059910611624204</v>
+        <v>-1.046458322904094</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.141017935747399</v>
+        <v>-1.127461889395796</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.155221346169142</v>
+        <v>-1.14397430118477</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.08849100000841759</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1636737113593796</v>
+        <v>-0.1754736306985052</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.7958552611920382</v>
+        <v>0.7835206254689595</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9514734102678659</v>
+        <v>0.9390875361980022</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6679035494487664</v>
+        <v>0.6555207977357753</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8531214064810868</v>
+        <v>0.8407105495900495</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5182561909042676</v>
+        <v>0.5059718498453663</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.09700756474563121</v>
+        <v>0.110188574040869</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.05586186668241311</v>
+        <v>-0.04266312772764991</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5385088707273411</v>
+        <v>-0.52510374307451</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.9729360581592914</v>
+        <v>-0.9594787644490737</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.489770172288374</v>
+        <v>-1.476317883568264</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.312872739135898</v>
+        <v>-1.299316692784295</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.727052417424602</v>
+        <v>-1.716667859278012</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1562816280881734</v>
+        <v>0.1461296197671089</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.0101843469673355</v>
+        <v>-0.02058122743273572</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.782568691837632</v>
+        <v>0.7717471813019472</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.7209678336477197</v>
+        <v>0.7101907900432565</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5947566295124602</v>
+        <v>0.583923169283544</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.6570961515768872</v>
+        <v>0.6462859175578757</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2074672735858627</v>
+        <v>0.1968276523356565</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3029126694721</v>
+        <v>-0.2897316601768622</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4503056442073188</v>
+        <v>-0.4371069052525556</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9980550193000397</v>
+        <v>-0.9846498916472086</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.289201432170529</v>
+        <v>-1.275744138460311</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.075552616077807</v>
+        <v>-2.062100327357697</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.020645239981668</v>
+        <v>-2.007089193630065</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.093031241970841</v>
+        <v>-2.08372935333874</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.0601036896747047</v>
+        <v>0.05099010367726464</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2937222751602278</v>
+        <v>-0.3029752702209123</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5289734410206037</v>
+        <v>0.5193069613624743</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5582075443830732</v>
+        <v>0.5485453697775995</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4137334559823316</v>
+        <v>0.4040311543043984</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6927361787488451</v>
+        <v>0.6829641645798148</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1353779127413333</v>
+        <v>0.1258148981955358</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4143818691945924</v>
+        <v>-0.4012008598993546</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5579581385312977</v>
+        <v>-0.5447593995765345</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.07777779094156</v>
+        <v>-1.064372663288729</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.241242923681931</v>
+        <v>-1.227785629971713</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.950047214726261</v>
+        <v>-1.936594926006151</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.916131718321871</v>
+        <v>-1.902575671970268</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.015543743322993</v>
+        <v>-2.007145554361401</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.01312335958004951</v>
+        <v>-0.02125447996370866</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3436885775223999</v>
+        <v>-0.3519446432832183</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5040594705522707</v>
+        <v>0.4954029784526028</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6165766709998692</v>
+        <v>0.6078906423273338</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3364307730326459</v>
+        <v>0.3277660632194568</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5767699413184317</v>
+        <v>0.5680512537303741</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2770351888156242</v>
+        <v>0.2684160878140815</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3874647056249145</v>
+        <v>-0.3742836963296767</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5668544892026404</v>
+        <v>-0.5536557502478772</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.864493486385264</v>
+        <v>-0.8510883587324329</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9113936141756085</v>
+        <v>-0.8979363204653907</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.784666336861754</v>
+        <v>-1.771214048141644</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.731361358224959</v>
+        <v>-1.717805311873356</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.815263037243</v>
+        <v>-1.807776054701286</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0</v>
+        <v>-0.00715291209358071</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4666023307736253</v>
+        <v>-0.4738044108122779</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3594064146381797</v>
+        <v>0.3518361690661322</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4727148351790191</v>
+        <v>0.4651152374865504</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.3304041504644673</v>
+        <v>0.322779799857166</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3480709014305745</v>
+        <v>0.340475916506044</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.133671147963625</v>
+        <v>0.1261404782784581</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6341511083902205</v>
+        <v>-0.6209700990949827</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5824114229829007</v>
+        <v>-0.5692126840281375</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6809394640799624</v>
+        <v>-0.6675343364271313</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9232726455940892</v>
+        <v>-0.9098153518838714</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.67806648937605</v>
+        <v>-1.66461420065594</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.647362813962452</v>
+        <v>-1.633806767610849</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.790492267048663</v>
+        <v>-1.783869689349743</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0273911436552865</v>
+        <v>-0.03361342246004284</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4046186546615402</v>
+        <v>-0.4109012658426394</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.04232250758253997</v>
+        <v>0.03582938760673926</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1205334946255832</v>
+        <v>0.1140240243624717</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2100615139849822</v>
+        <v>0.2034520642503566</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1333960797837861</v>
+        <v>0.1268455605934378</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.07499666225055535</v>
+        <v>-0.08148656399718845</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8092455057330596</v>
+        <v>-0.8155320030262203</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6552686810590274</v>
+        <v>-0.6420699421042642</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8604637335179888</v>
+        <v>-0.8470586058651577</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.029387606026184</v>
+        <v>-1.015930312315966</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.711593484868494</v>
+        <v>-1.698141196148384</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.737724125910134</v>
+        <v>-1.724168079558531</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.790896503446106</v>
+        <v>-1.785068043807094</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1647043446621694</v>
+        <v>0.1595145110061722</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2174319937598881</v>
+        <v>-0.2226539405564552</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1227762626664415</v>
+        <v>-0.1280717581007806</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1941986969457972</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2469378006755605</v>
+        <v>0.2414716476497176</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1922243580484206</v>
+        <v>0.1868026885939429</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.110040434361224</v>
+        <v>-0.1153716522776165</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5250871383476436</v>
+        <v>-0.5303273821752086</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4849065860813795</v>
+        <v>-0.4717078471266163</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7616759532340964</v>
+        <v>-0.7482708255812653</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9664292775516756</v>
+        <v>-0.9529719838414579</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.640309189346205</v>
+        <v>-1.626856900626095</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.622115233680653</v>
+        <v>-1.60855918732905</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.691205588814618</v>
+        <v>-1.686364852448222</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2036571154746767</v>
+        <v>0.1993647607866436</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2416658284488165</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1791356489548264</v>
+        <v>0.1746846014807559</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4866025247855603</v>
+        <v>0.4820613126544941</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6048947101710311</v>
+        <v>0.6002697498710745</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4725134200837431</v>
+        <v>0.4679522511161736</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3094564281727159</v>
+        <v>0.3049380287231997</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.07615153972908217</v>
+        <v>-0.08058689511592121</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1691411891871368</v>
+        <v>-0.1559424502323736</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4434506352515299</v>
+        <v>-0.4300455075986989</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.584224433017603</v>
+        <v>-0.5707671393073852</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9337184349811949</v>
+        <v>-0.9202661462610848</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.03407541316858</v>
+        <v>-1.020519366816977</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.150552417424599</v>
+        <v>-1.146671112623714</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.003248160234115005</v>
+        <v>-0.006564793358734278</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2402776336573282</v>
+        <v>-0.2436264218173179</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.01483080588377561</v>
+        <v>-0.01827447453679554</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1620945472173361</v>
+        <v>0.1586038249059314</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.6072126860449529</v>
+        <v>0.6035515081213276</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.3168418249118545</v>
+        <v>0.3132853109283573</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1277620080355248</v>
+        <v>0.1242553776595088</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.08085420910354912</v>
+        <v>-0.08432928377912674</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2462166763171822</v>
+        <v>-0.2496474918422891</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4004265814661423</v>
+        <v>-0.3870214538133112</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5749227197020232</v>
+        <v>-0.5614654259918055</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.7658109063104632</v>
+        <v>-0.7691447622900398</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7320703598703844</v>
+        <v>-0.7185143135187815</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.8892723689837965</v>
+        <v>-0.886241133025905</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2772351665760482</v>
+        <v>0.2747657876474676</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.04507334255061579</v>
+        <v>0.04259523360557438</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1205344867574638</v>
+        <v>0.1180156332044788</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.03879115040209058</v>
+        <v>0.0363001709189561</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3977834257019168</v>
+        <v>0.3951644712179458</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.284100102218936</v>
+        <v>0.2815257277062528</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.04419835388679161</v>
+        <v>0.04168705017484342</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1796081830337499</v>
+        <v>-0.1820784449362165</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2249478824551403</v>
+        <v>-0.2274093302612883</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3345433038829597</v>
+        <v>-0.3211381762301286</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4823328002312905</v>
+        <v>-0.4688755065210728</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5745034692403195</v>
+        <v>-0.5769069240888598</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4944247898832757</v>
+        <v>-0.4968715495031333</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7132981414838966</v>
+        <v>-0.7111034552316156</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3729</v>
+        <v>3730</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1137591758249457</v>
+        <v>-0.1152384042312207</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2938324734256383</v>
+        <v>-0.2953106797479137</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1125077130720484</v>
+        <v>-0.1140465492732545</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.155016856909107</v>
+        <v>-0.1565413556690842</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.03652837962307132</v>
+        <v>-0.03810088280569346</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.07245417407806087</v>
+        <v>-0.07400928437107979</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1961439297514005</v>
+        <v>-0.1976691604769059</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3540588590520528</v>
+        <v>-0.3555560674969058</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2128056731439116</v>
+        <v>-0.2143432637132818</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2322770532415035</v>
+        <v>-0.2188719255886724</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2226681053189949</v>
+        <v>-0.2092108116087772</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5216926847222254</v>
+        <v>-0.5231713516435903</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4176249561352137</v>
+        <v>-0.4191443986052548</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6087063460918003</v>
+        <v>-0.6072876831495648</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3914</v>
+        <v>3915</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.002740997161396308</v>
+        <v>0.001895275806361951</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04131766565830475</v>
+        <v>-0.04217853725075571</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1165982748370809</v>
+        <v>-0.117446756760863</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.02751753489632591</v>
+        <v>0.02663400016888318</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.01290997230810831</v>
+        <v>0.01202104211905919</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.05819668505540676</v>
+        <v>-0.05906312330961327</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1800343793431267</v>
+        <v>-0.1808715440996451</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2505565619668317</v>
+        <v>-0.2513837076049015</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.06783210732763933</v>
+        <v>-0.06870728816859639</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.07569082987470921</v>
+        <v>-0.06228570222187813</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.04020888592563665</v>
+        <v>0.03929185314733274</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1153163808397508</v>
+        <v>-0.1161936052056518</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1380923959333344</v>
+        <v>-0.1389710230632843</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2571686667858657</v>
+        <v>-0.2563996776438273</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4089</v>
+        <v>4090</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2378908927532564</v>
+        <v>-0.2381076443812589</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1537924209791086</v>
+        <v>-0.1540382367413144</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1695561703880486</v>
+        <v>-0.1698003376215098</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.001643124537658025</v>
+        <v>-0.0019277011883716</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.03863207590890738</v>
+        <v>-0.03891058745547582</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04517709701983108</v>
+        <v>-0.04545258727355161</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.0189058253574359</v>
+        <v>-0.0191883099916339</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1063441252927078</v>
+        <v>-0.1066078485433266</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.04156294669143534</v>
+        <v>0.0412626415002677</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.04655625665495933</v>
+        <v>0.05996138430779041</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1487726794606559</v>
+        <v>0.1484437100446598</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.07472933350018707</v>
+        <v>0.07441848720753086</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1327922649690407</v>
+        <v>0.1324648925930276</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.01934576543144573</v>
+        <v>-0.01911408246260038</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/stoch/stoch_7.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_7.xlsx
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 4.638</t>
+          <t>X ≈ 4.646</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>90</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.386516694854684</v>
+        <v>6.357477822991875</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.566911849861903</v>
+        <v>2.565749478688829</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.04257774369965972</v>
+        <v>-0.0427295908472729</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.304129705265616</v>
+        <v>2.303652920659012</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.209881968266615</v>
+        <v>-8.161497239760642</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.13289069417295</v>
+        <v>-10.10903729808272</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.001549485025812</v>
+        <v>-7.953661938805389</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.250942082764631</v>
+        <v>-6.201796118947811</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.984106387777111</v>
+        <v>-2.910954164846345</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.834028905611753</v>
+        <v>-3.734794115066634</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.149867155195388</v>
+        <v>-5.050046595117358</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.66959438639729</v>
+        <v>-10.54597584946722</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-8.870672878573522</v>
+        <v>-8.722027562631496</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.647204275344471</v>
+        <v>-8.475205515778818</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 7.947</t>
+          <t>X ≈ 7.954</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.383956482597895</v>
+        <v>4.354909865594671</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.865320739442012</v>
+        <v>1.864154626331349</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.216522807082775</v>
+        <v>4.216404925097926</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.432426428664627</v>
+        <v>3.431959550238346</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.21936841257149</v>
+        <v>10.26786224514013</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.856649679199023</v>
+        <v>6.880593189750826</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.026455121723529</v>
+        <v>4.074395245528564</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.561117675704189</v>
+        <v>3.61029970463364</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.9149108003093</v>
+        <v>9.988103795249152</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.235323053329211</v>
+        <v>7.334583596710317</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.949305955445766</v>
+        <v>8.049149948975739</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.902678983211054</v>
+        <v>9.026321118541098</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.567623021776953</v>
+        <v>7.716277667743149</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>10.54749501109743</v>
+        <v>10.71949377066409</v>
       </c>
     </row>
     <row r="8">
@@ -676,101 +676,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.565642190778242</v>
+        <v>3.477110287868676</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.961938452791685</v>
+        <v>1.885897965834801</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.323865884816044</v>
+        <v>2.24126627186223</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.721158117500181</v>
+        <v>4.622649016827729</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.964447141852617</v>
+        <v>7.883144954956208</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.751742398576241</v>
+        <v>6.315279904771074</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.132128780670186</v>
+        <v>2.504127595429708</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.935503338698275</v>
+        <v>4.291780401055348</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.118877689797635</v>
+        <v>3.504909473724396</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.784268098750601</v>
+        <v>4.185083605211091</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.309799890321628</v>
+        <v>1.72835065826996</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9269542551714096</v>
+        <v>-0.4674407529506581</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5899018707350976</v>
+        <v>-0.1109716724146139</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.121951750092798</v>
+        <v>-0.6138855491951958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 14.56</t>
+          <t>X ≈ 14.57</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>129</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.6014740000252345</v>
+        <v>0.972968352886447</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.617933096461414</v>
+        <v>4.033558531861502</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.222940549524239</v>
+        <v>3.641662745711997</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.994833536517888</v>
+        <v>8.411829355654362</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.362166550883032</v>
+        <v>4.831976321869156</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0191811478115298</v>
+        <v>0.4636855796073078</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3558611328024597</v>
+        <v>-0.3699566646541115</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.658221330361009</v>
+        <v>-2.383008783962083</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.267968489542064</v>
+        <v>-3.968981222517485</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.343467770366736</v>
+        <v>-4.018606805838644</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.225175230265087</v>
+        <v>-1.899926273175666</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4162706369462938</v>
+        <v>-1.067425171077431</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.611451658260599</v>
+        <v>-2.237793081717676</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.386222363200275</v>
+        <v>-1.989417402083227</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>136</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.07699569263836281</v>
+        <v>0.4011678537757106</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.783686152723696</v>
+        <v>0.9948108983268611</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.390258075153071</v>
+        <v>1.331824444090742</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.146968998321128</v>
+        <v>-2.202244727738083</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.68426352922112</v>
+        <v>-2.699230623246351</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.5479466922439826</v>
+        <v>0.5082796491975614</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.939044777485634</v>
+        <v>-3.961841308487067</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.938303654772341</v>
+        <v>-3.295080433305507</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7973930552505308</v>
+        <v>-1.129570268360709</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.646551629050087</v>
+        <v>-1.959170912740603</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3822293211077863</v>
+        <v>0.03933580332962094</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.287377733103405</v>
+        <v>-2.843720119306063</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.03297777054122264</v>
+        <v>0.1156668676433057</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9279591233479962</v>
+        <v>1.099957882914659</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.148030016393889</v>
+        <v>2.049039833468171</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.791092199792317</v>
+        <v>-1.066658707268488</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.64140897547923</v>
+        <v>-0.7001760804115023</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6786478324478011</v>
+        <v>0.9550671478932387</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.724503872891148</v>
+        <v>-4.87290851929324</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.748921914620048</v>
+        <v>-6.124580093471664</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.903276471247267</v>
+        <v>1.434348348048466</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.306630915447407</v>
+        <v>4.777666487517251</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.924936481471384</v>
+        <v>2.454671157397307</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.020149634914389</v>
+        <v>-0.663300129300282</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.323054780872418</v>
+        <v>-5.016999164373587</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4161492009863395</v>
+        <v>-1.144597035526388</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.386352045537144</v>
+        <v>-3.065918358858298</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.6110285647508391</v>
+        <v>-0.5277924538616077</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>131</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.992743675418495</v>
+        <v>3.942597324510992</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.460997801425847</v>
+        <v>-4.524578697626879</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.617663287303557</v>
+        <v>-5.684846845091862</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-7.771980106004591</v>
+        <v>-7.839471966442289</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.026022988050492</v>
+        <v>-5.291998347799243</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.125095617740122</v>
+        <v>2.606466955821226</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.040897983202903</v>
+        <v>2.543350953301626</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.9491374855726988</v>
+        <v>0.546538018416399</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5139774430237338</v>
+        <v>1.693084145267932</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3344595261004955</v>
+        <v>-0.235471129709353</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5390456345909982</v>
+        <v>0.3234592120715405</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.03059335059816</v>
+        <v>-1.144561385713686</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.214482966082926</v>
+        <v>-2.302714605537638</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.226508770680006</v>
+        <v>-2.054510011113344</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>153</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.030710989876262</v>
+        <v>3.688337621554354</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.758945509249344</v>
+        <v>1.459107911217252</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.57897317789655</v>
+        <v>6.286626397617063</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.710046513693925</v>
+        <v>6.418342439681389</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.562381494985743</v>
+        <v>3.320160861831774</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.259837508547193</v>
+        <v>1.633825776264601</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.479912437881829</v>
+        <v>2.88023604544032</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.667085716410256</v>
+        <v>3.067854434468977</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.607212616734074</v>
+        <v>3.030841908638251</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.8016739575402809</v>
+        <v>0.2481966723012334</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.250425735213732</v>
+        <v>0.6974075824422457</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.02108285149372335</v>
+        <v>-0.5509862620073918</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.74800951907531</v>
+        <v>-2.252760773171737</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.091357816158286</v>
+        <v>0.6097618044831208</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.477201013201622</v>
+        <v>-2.853116009808275</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.385930732639778</v>
+        <v>-1.751852527859256</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.261983575441057</v>
+        <v>1.902350383765921</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.739266096804464</v>
+        <v>3.384449334999395</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.856566070312638</v>
+        <v>1.540758122347221</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.1757534570066</v>
+        <v>3.840174939288538</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.11370515539992</v>
+        <v>5.806087197188745</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.62669377520254</v>
+        <v>3.986663941221678</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.543344404136626</v>
+        <v>1.923768709640989</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.02099006315086172</v>
+        <v>0.416605889901696</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.191459782835025</v>
+        <v>3.588034407011556</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.201399619166224</v>
+        <v>1.325286050084131</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5692145386765759</v>
+        <v>-0.4205766140031457</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.695252323393028</v>
+        <v>-1.523253563826366</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>111</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-10.11016569969016</v>
+        <v>-10.61348459875055</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.732667047800227</v>
+        <v>-3.223405124492132</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4645537775687387</v>
+        <v>0.8829847861342088</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5939132514536851</v>
+        <v>1.016113339889714</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.856084999923084</v>
+        <v>2.320035286326551</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3554433672925086</v>
+        <v>0.7940084951301785</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2709856702437534</v>
+        <v>0.3204373684466688</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1947185451041449</v>
+        <v>-0.1452151691092354</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2555524447067086</v>
+        <v>-0.1821757633908518</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.2039022477783448</v>
+        <v>-0.1049532034943397</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.3085396392025</v>
+        <v>-1.209640167824695</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.326685172593571</v>
+        <v>2.450988978386526</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.006842102774051</v>
+        <v>1.155476772711054</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.232675604534904</v>
+        <v>1.404674364101567</v>
       </c>
     </row>
     <row r="16">
@@ -1095,150 +1095,150 @@
         <v>139</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.487741051162182</v>
+        <v>-2.519763960494934</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.239728302608427</v>
+        <v>-1.243338665745355</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.62092861697915</v>
+        <v>1.240421263746626</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.619347270820576</v>
+        <v>4.249977204844711</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.085780036964813</v>
+        <v>3.755687469073472</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.817705073383408</v>
+        <v>5.468847190297339</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.580615898804645</v>
+        <v>3.249155079006101</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.834088446929663</v>
+        <v>3.498933575200844</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.056681963904659</v>
+        <v>2.742282292041843</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.491715123753664</v>
+        <v>1.189369134365371</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.006314009200814</v>
+        <v>1.703636292899738</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.322710337340418</v>
+        <v>1.040599074701461</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.130923417408752</v>
+        <v>-4.395614346689413</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.128974781409617</v>
+        <v>1.300973540976443</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 41.03</t>
+          <t>X ≈ 41.05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.879122424629799</v>
+        <v>-2.894325746968612</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.38569559893353</v>
+        <v>-1.378484189217389</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2196054439209476</v>
+        <v>-0.2240052472661276</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.540738217343332</v>
+        <v>-5.518283060866281</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.767247429662632</v>
+        <v>-2.133213703520966</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.028915789161481</v>
+        <v>-3.410815781601258</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.671245469423766</v>
+        <v>-5.021859467726117</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.138618142394556</v>
+        <v>-5.487692228109459</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.980922671096693</v>
+        <v>-6.299858635695877</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.050637959042049</v>
+        <v>-6.348493418061423</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-10.93958254027056</v>
+        <v>-11.20379665629483</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.786684115393193</v>
+        <v>-8.044854725131664</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.96206914567685</v>
+        <v>-2.238462264098594</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.768732053122754</v>
+        <v>-9.741355386579528</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 44.34</t>
+          <t>X ≈ 44.36</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>114</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.974456541289705</v>
+        <v>-6.010071661465538</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.581583161274267</v>
+        <v>-0.5837034353241251</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.852825395590784</v>
+        <v>-1.85471341494145</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.222005030568887</v>
+        <v>-5.232638175584789</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.25899089933035</v>
+        <v>-2.214813050726562</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2129197834651819</v>
+        <v>-0.187641566995346</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5779471041158217</v>
+        <v>0.6288953262355363</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.637392100692665</v>
+        <v>-1.591323399060094</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.8029770805217</v>
+        <v>1.880475921627671</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.832129029063132</v>
+        <v>1.933840323269031</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.628477472242857</v>
+        <v>1.729699875732742</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.539914325930702</v>
+        <v>2.665059595553579</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5096995875829009</v>
+        <v>-0.3616772783784796</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.54778907066661</v>
+        <v>-5.375790311099948</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.963473002336173</v>
+        <v>2.93877354834202</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.892413669436934</v>
+        <v>-5.903749877646668</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.569917409342615</v>
+        <v>-3.575658267177111</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.811006243581254</v>
+        <v>3.822660955145906</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.181410334041502</v>
+        <v>4.244517092814313</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.758701363635382</v>
+        <v>1.79002988436072</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9.832159089786003</v>
+        <v>9.911191976953432</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.210444455639283</v>
+        <v>1.263541034751292</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.385658338936864</v>
+        <v>-3.318886119839632</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.93355731906243</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.09921963548909929</v>
+        <v>0.198599397263834</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.041858389799309</v>
+        <v>1.165857043719839</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.530956045714859</v>
+        <v>1.679790026246721</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.06134568948618124</v>
+        <v>0.1106530700802679</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.82840694482659</v>
+        <v>-3.831596145744015</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7778761373290166</v>
+        <v>0.7734557237799891</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.278333576849896</v>
+        <v>1.263339982683597</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.411214536368611</v>
+        <v>1.393945230747562</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.539489581401746</v>
+        <v>3.560687647922919</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.619088230204682</v>
+        <v>5.603384671166829</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.479126166287003</v>
+        <v>-2.421873187970533</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.574614611280332</v>
+        <v>-2.002750196141285</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.63570739677165</v>
+        <v>-2.039722805278082</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.375310688678212</v>
+        <v>-3.748507138305456</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.689163798205101</v>
+        <v>-3.067691833628956</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.33229431261244</v>
+        <v>-5.664392352901437</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.077370326486886</v>
+        <v>-3.404683022828088</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1749820531229531</v>
+        <v>-0.5007709041755604</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>109</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.762119761673752</v>
+        <v>-4.359060827459523</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.877701557383503</v>
+        <v>-0.4637612114683947</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.274896535178719</v>
+        <v>-0.850293855724928</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.80526117079183</v>
+        <v>-4.385799696643765</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.682323157043619</v>
+        <v>-1.635382823782848</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.300670581086983</v>
+        <v>-2.280028497624691</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.214145139612476</v>
+        <v>-4.175546972171041</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1040096478203196</v>
+        <v>-0.05422376925162808</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.910202244098571</v>
+        <v>-2.843489956370291</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8195623301065069</v>
+        <v>0.9198374261176951</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.615896317611714</v>
+        <v>0.7156969785813914</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.015771604636349</v>
+        <v>-2.8958610546957</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.898553194864228</v>
+        <v>4.048430560025075</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.37318308449192</v>
+        <v>1.545181844058582</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>113</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.679802313397381</v>
+        <v>-4.715658651245278</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.538565269637566</v>
+        <v>2.541757407670332</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.388112606918604</v>
+        <v>-1.389434967168604</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.141041214117159</v>
+        <v>-2.144753476611882</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.971593265274777</v>
+        <v>-7.943737130838343</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.028158837743646</v>
+        <v>-5.016084355382048</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.993897413756088</v>
+        <v>-5.961696196819695</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.575970177254128</v>
+        <v>-5.542573204990653</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.873206331433394</v>
+        <v>-3.809634309702666</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.372291890568938</v>
+        <v>-7.288330147155023</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.463568575038082</v>
+        <v>-8.377426346903498</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-9.317390568150458</v>
+        <v>-9.204215361750997</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.435472888385455</v>
+        <v>-4.289638775040679</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-12.17719444250329</v>
+        <v>-12.00519568293662</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.028030331929479</v>
+        <v>4.005355288517656</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.422632442078701</v>
+        <v>2.426166703172868</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5808389931156839</v>
+        <v>0.5846578385928609</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.901265562582303</v>
+        <v>-2.90786749482394</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5476011717554385</v>
+        <v>-0.498565911138094</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.418589662227426</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.668607656571773</v>
+        <v>-4.634262568501399</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-6.577392511621305</v>
+        <v>-6.549370691203499</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.641158208783686</v>
+        <v>-6.586343300340459</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.214878878923045</v>
+        <v>-8.134809562314693</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.252889001258005</v>
+        <v>-6.165036966372689</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-11.28896559473655</v>
+        <v>-11.17933399712358</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-13.16451756796122</v>
+        <v>-13.02376728600624</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.874257415441598</v>
+        <v>-7.702258655875099</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>107</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.007527520363695</v>
+        <v>-2.039647131347664</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.406282088987801</v>
+        <v>-6.4222672370257</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.94065925239687</v>
+        <v>-4.95205304911984</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.947658242979387</v>
+        <v>-2.95527369826457</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.483566151592143</v>
+        <v>-3.444522839216283</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.469648322084915</v>
+        <v>1.501159875864332</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.406844191442104</v>
+        <v>-1.363234531118238</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.801636699708254</v>
+        <v>-2.76364673075382</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.863640558399609</v>
+        <v>-2.800619339890396</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.779656688201285</v>
+        <v>-2.68986848145326</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.186828791378737</v>
+        <v>-0.0902706112322349</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.781025548839466</v>
+        <v>0.9024755653846768</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.3599543632597033</v>
+        <v>0.507317638821057</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3502156979825699</v>
+        <v>-0.1782169384156873</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>112</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.582700382488177</v>
+        <v>-1.614432489053009</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.406589289999957</v>
+        <v>-1.412343780251369</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.02527353395633014</v>
+        <v>-0.02317254464438179</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.883737464908343</v>
+        <v>1.892857142857238</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.320654936888097</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.915164955947603</v>
+        <v>-1.895035050704521</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.341049305885093</v>
+        <v>3.401451717212979</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2095385607684861</v>
+        <v>0.2570475282583047</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.740911426059867</v>
+        <v>-0.6727822237357444</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.75607059254267</v>
+        <v>3.860532052592134</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.227112476807193</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.806442955090695</v>
+        <v>1.928844056706858</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.278186843768736</v>
+        <v>2.426543272999972</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.503589375448676</v>
+        <v>2.675588135015339</v>
       </c>
     </row>
     <row r="26">
@@ -1615,98 +1615,98 @@
         <v>127</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2738278234395537</v>
+        <v>0.2453846892464284</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.897046623692233</v>
+        <v>-2.907469259299653</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.511613414771688</v>
+        <v>-2.517379149703707</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.382349382227808</v>
+        <v>-2.388638920134994</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2203627713109597</v>
+        <v>0.2717182381257857</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.190401870350001</v>
+        <v>-4.17990569187419</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.704130820777003</v>
+        <v>-2.665758631493446</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.518300745140159</v>
+        <v>-5.493796116286319</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8732403212841646</v>
+        <v>-0.8063592766041268</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.99097580657314</v>
+        <v>3.09422159139978</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.141412662009003</v>
+        <v>-1.046926730151959</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4656204111737878</v>
+        <v>0.5860431568191373</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.04405905441135616</v>
+        <v>0.1908852302552262</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.30687181690228</v>
+        <v>-1.134873057335703</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 74.14</t>
+          <t>X ≈ 74.13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5746667361152902</v>
+        <v>-0.6003706354996439</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.8695482444657685</v>
+        <v>0.8686928377251704</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.418529201019474</v>
+        <v>-6.391274266498066</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.053692081525789</v>
+        <v>-7.028898582333703</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.229986493622647</v>
+        <v>-2.174636272904031</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.230916022439722</v>
+        <v>-4.191927089962881</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.31776586787403</v>
+        <v>-4.252583179188342</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.792055277478354</v>
+        <v>-4.718415939571592</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.121324696944043</v>
+        <v>-2.465312212830611</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.504710547172905</v>
+        <v>-4.815858350897507</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.17717235397938</v>
+        <v>-3.493281241181684</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.376417376293546</v>
+        <v>-2.671755725190842</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.568970389057611</v>
+        <v>-3.830272430380532</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.809597437738141</v>
+        <v>-2.054510011113251</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>174</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.252773705521292</v>
+        <v>3.229225471156397</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.796676570794844</v>
+        <v>2.800265352742557</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.751862558782818</v>
+        <v>-2.76068907049504</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.383876718475896</v>
+        <v>1.389983579638688</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.8470731104204603</v>
+        <v>0.9007344386868326</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.144149951047524</v>
+        <v>1.173519957505761</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6552139107377286</v>
+        <v>-0.6112740627541839</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.036834592443071</v>
+        <v>4.095306969965854</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.257929854312728</v>
+        <v>2.334196429794638</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.8399781977776897</v>
+        <v>0.9356552053015008</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.06242863859272063</v>
+        <v>0.1568021140872418</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4765780702892997</v>
+        <v>-0.3597437922260198</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2487119715671895</v>
+        <v>0.394523568566477</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1031429726629867</v>
+        <v>0.06885578690367566</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>161</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9285963295522208</v>
+        <v>0.9024031453120926</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6696594991699598</v>
+        <v>-0.6744858270206677</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.735394352831932</v>
+        <v>5.756224815180353</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.861701234498682</v>
+        <v>5.89130434782615</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.179868604206661</v>
+        <v>7.265409244141239</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.622353015806723</v>
+        <v>5.674840725693016</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.014616467111594</v>
+        <v>8.098656686157149</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.17276662539809</v>
+        <v>8.253941938196085</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.639120746418179</v>
+        <v>5.732497279369781</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.417794794252949</v>
+        <v>5.529786710977298</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.456957229222809</v>
+        <v>6.567882288285936</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.07749151623721</v>
+        <v>12.216111137452</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.803582460119785</v>
+        <v>9.957599173621098</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.792409251225074</v>
+        <v>8.964408010791807</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.614655623841941</v>
+        <v>-3.347862152350643</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2113896377622027</v>
+        <v>0.04646101744425124</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.397374973648418</v>
+        <v>-3.120033123956304</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.499236169792965</v>
+        <v>-5.468253968253975</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6793791236579878</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.383911322910372</v>
+        <v>-2.351384257053574</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.033648101388543</v>
+        <v>-2.967595901834677</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1540619375293346</v>
+        <v>-0.1000953288846844</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.897588385083949</v>
+        <v>-1.803734604688088</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3616721334168886</v>
+        <v>0.1502145922746081</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4070299843219516</v>
+        <v>-0.6094814108170326</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.864664034109623</v>
+        <v>1.670907548770138</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.583838650431893</v>
+        <v>4.053527399984091</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.687377497439044</v>
+        <v>3.191461150888287</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.809703633658849</v>
+        <v>4.757176929678309</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.652417177533309</v>
+        <v>4.639288884068151</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.313565888304545</v>
+        <v>2.309089606496805</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.931988865256436</v>
+        <v>-1.929958391123463</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.954484934109267</v>
+        <v>-2.904644425279251</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2271176980209333</v>
+        <v>-0.2046744404409253</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.286214840579724</v>
+        <v>-1.236204316074151</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.755630315422138</v>
+        <v>-1.702037076457437</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1272540842510494</v>
+        <v>0.2027378872212964</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7337951041930779</v>
+        <v>0.835219986017961</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.011553067010126</v>
+        <v>1.116516431685724</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.503383248085804</v>
+        <v>2.630993848662264</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.057720760345724</v>
+        <v>3.206709708506203</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.1116033127309</v>
+        <v>1.999443890909923</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>221</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-6.305734799173365</v>
+        <v>-6.33436831964142</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-5.650474263596202</v>
+        <v>-5.664204140291687</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.794320158826963</v>
+        <v>-3.808293866683336</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.211615488072979</v>
+        <v>-3.225921137685809</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.909163745701726</v>
+        <v>-6.882591093117405</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.708855158141994</v>
+        <v>-5.704828198732841</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.984997073016814</v>
+        <v>-3.955529536827108</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.093277471035826</v>
+        <v>-3.063896233862025</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.0009500841613387934</v>
+        <v>0.06655197148081271</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.40937993084632</v>
+        <v>1.505166829579828</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.913949402509402</v>
+        <v>4.015958508740596</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.330519122814799</v>
+        <v>0.4542157438430436</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.8153456450669978</v>
+        <v>0.9640351928448041</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.041081295293566</v>
+        <v>1.213080054860171</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.360201256984432</v>
+        <v>2.828946653379106</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.051165390152171</v>
+        <v>5.277944032722004</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1872910314248415</v>
+        <v>-0.1859516295403409</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.711423959001337</v>
+        <v>3.707373271889381</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.020005093347265</v>
+        <v>1.067586496528868</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2401297335556265</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1533651748468472</v>
+        <v>0.2044471089180604</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.83737164417591</v>
+        <v>1.889151982943304</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.854665976801179</v>
+        <v>2.927448191010811</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.080284737029224</v>
+        <v>3.178888427400139</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.038926436615384</v>
+        <v>5.125285614272634</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.093757474288445</v>
+        <v>7.871624394648272</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.511444458812875</v>
+        <v>5.325928833675889</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.818261190120452</v>
+        <v>6.650242512895552</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>175</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.561077824981879</v>
+        <v>-5.652968967744144</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.618485649981714</v>
+        <v>-2.664717481471413</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.310186617380616</v>
+        <v>-1.344169755500396</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.6383177892914205</v>
+        <v>-0.6428571428571459</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.167414476051398</v>
+        <v>-1.132106283809065</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2730005537675453</v>
+        <v>0.2835363778670086</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.603623895549362</v>
+        <v>3.651451717212964</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.154940984434077</v>
+        <v>3.185618956829629</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.501754378563987</v>
+        <v>2.577217776264263</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.790280149250123</v>
+        <v>2.896246338306405</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.592197854751653</v>
+        <v>2.692105890770328</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.340861721392699</v>
+        <v>4.464558342420951</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.206425153793568</v>
+        <v>6.355114701571395</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.289303661162954</v>
+        <v>5.461302420729616</v>
       </c>
     </row>
   </sheetData>
@@ -2210,261 +2210,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 2.983</t>
+          <t>X &gt; 2.991</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2137292923578542</v>
+        <v>-0.2125188270751721</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01665183885000232</v>
+        <v>0.01663326894548334</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.09662960591419534</v>
+        <v>-0.09636769135194356</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.05072008957578333</v>
+        <v>-0.05057351407717192</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.03891058745547582</v>
+        <v>-0.03986972990301041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0210444837831929</v>
+        <v>-0.02151300313173721</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0296398150083661</v>
+        <v>0.02850831048578328</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08875234681686806</v>
+        <v>0.08743511436912144</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2122445662682253</v>
+        <v>0.21006969900656</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1576892123068134</v>
+        <v>0.1550878866216507</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1377920455071404</v>
+        <v>0.1352311301422233</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1615133259602075</v>
+        <v>0.1583662410069877</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1952480668218612</v>
+        <v>0.1914612372595599</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2636948850039289</v>
+        <v>0.2592118283951237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 6.292</t>
+          <t>X &gt; 6.3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3999</v>
+        <v>4010</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3622719627377364</v>
+        <v>-0.3599751109918827</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.04074336019753133</v>
+        <v>-0.04057881556247622</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.0978460769317735</v>
+        <v>-0.09757153899419535</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1037174593021533</v>
+        <v>-0.1034115138592782</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1449822418200952</v>
+        <v>0.1424111867770819</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2065289493088471</v>
+        <v>0.204890285283625</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2103867609956325</v>
+        <v>0.2076592637117756</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2314311411810479</v>
+        <v>0.2285899300794796</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2841804467043474</v>
+        <v>0.2801176161503989</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2475253289891484</v>
+        <v>0.2423919714475744</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2567941280435804</v>
+        <v>0.2516089344497985</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4052741897041869</v>
+        <v>0.3986133203443103</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3992822966507106</v>
+        <v>0.3915146018456426</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4642402524536351</v>
+        <v>0.455246132877825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 9.601</t>
+          <t>X &gt; 9.608</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3890</v>
+        <v>3901</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4952639680183424</v>
+        <v>-0.4917163215655691</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.09415235424913249</v>
+        <v>-0.0938000268330228</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2187371330648276</v>
+        <v>-0.2181107429383218</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2028022109187049</v>
+        <v>-0.2021952734046835</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1373077562806557</v>
+        <v>-0.1405096451535996</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.02018880546360435</v>
+        <v>0.01836077577659267</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1034583673402807</v>
+        <v>0.09961665360717831</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.138131441370497</v>
+        <v>0.1340997056687101</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01432193551079308</v>
+        <v>0.008861401456279339</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.05172328478527533</v>
+        <v>0.04422512008802215</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.04124559611894085</v>
+        <v>0.03373352543074759</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1671721016599079</v>
+        <v>0.1575417617686981</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1984213354582209</v>
+        <v>0.186849343147145</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.181701751504491</v>
+        <v>0.1684471089048145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 12.91</t>
+          <t>X &gt; 12.92</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3758</v>
+        <v>3768</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6379035669968331</v>
+        <v>-0.6318049465801039</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1663726806273544</v>
+        <v>-0.1636779018396126</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.308046233213922</v>
+        <v>-0.304919963471356</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3757566450196279</v>
+        <v>-0.372498959869894</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4218824360447826</v>
+        <v>-0.4237225065693622</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2162574623093789</v>
+        <v>-0.2039030894453475</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03220118411526585</v>
+        <v>0.01474405401524592</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.004748500857658655</v>
+        <v>-0.01265494732663086</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.09472579188830821</v>
+        <v>-0.1145394461052049</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07938260011186316</v>
+        <v>-0.1019357553157505</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.003312457855180639</v>
+        <v>-0.0260817820712802</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2056033627300806</v>
+        <v>0.179601919533475</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2261112405187617</v>
+        <v>0.1973616029851897</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2274926674733067</v>
+        <v>0.1960612924311675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 16.22</t>
+          <t>X &gt; 16.23</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3629</v>
+        <v>3639</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6819596998559732</v>
+        <v>-0.6886930355142056</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3008933323893928</v>
+        <v>-0.3124669922346186</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4335621590814398</v>
+        <v>-0.4448235549757982</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6733058688880078</v>
+        <v>-0.6838972431077721</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.59194094233127</v>
+        <v>-0.6100333471488</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2246265944960939</v>
+        <v>-0.2275686399558623</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.02069604953807413</v>
+        <v>0.02838142491613382</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.0638620605785718</v>
+        <v>0.07137243517569658</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.01807341119720007</v>
+        <v>0.0220978138995136</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.03664577877017194</v>
+        <v>0.03690748884953621</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.04012107690395084</v>
+        <v>0.04034469205690527</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2277091070007558</v>
+        <v>0.2238081560514189</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2914310569812955</v>
+        <v>0.2836861301428257</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2848553676543233</v>
+        <v>0.2735349806950751</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3493</v>
+        <v>3503</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7115096378402939</v>
+        <v>-0.7310056478303366</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3820564614977258</v>
+        <v>-0.3632205729129936</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5045726233974719</v>
+        <v>-0.5137998975030769</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6159287759584586</v>
+        <v>-0.6249491249491257</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5104763354555217</v>
+        <v>-0.5289226336034716</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2547067453683169</v>
+        <v>-0.2561371147845435</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1748686096512273</v>
+        <v>0.1832972946685842</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1807514213823893</v>
+        <v>0.202071147740206</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.04982360857392365</v>
+        <v>0.06681002034752481</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1021810915281307</v>
+        <v>0.1144029677579752</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.05656529509163732</v>
+        <v>0.04038386101691316</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3645690584047543</v>
+        <v>0.3429014604900829</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3040619188602207</v>
+        <v>0.290209287350919</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.2598161146413389</v>
+        <v>0.2414500492928866</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3364</v>
+        <v>3372</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8211649931899458</v>
+        <v>-0.8390086009887341</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3280238781921341</v>
+        <v>-0.335892460338691</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4993253316559247</v>
+        <v>-0.5065593043948269</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6655721714651222</v>
+        <v>-0.6863317262962099</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3872273603279339</v>
+        <v>-0.3601616160989209</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04401894607180168</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1085889978361578</v>
+        <v>0.1346947774702585</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.01581173400833791</v>
+        <v>0.02431225405372572</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.06042893619532919</v>
+        <v>-0.02595682691033829</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1452193387668572</v>
+        <v>0.1446162256804584</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2245114870652927</v>
+        <v>0.2368598919558664</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3945074220972131</v>
+        <v>0.4006898065690123</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4072317765912743</v>
+        <v>0.4205926567617766</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2932105747012628</v>
+        <v>0.2713346186621806</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3233</v>
+        <v>3241</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.01622284521212</v>
+        <v>-1.032279312571717</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1605572577332381</v>
+        <v>-0.1665873393622164</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.291932114152111</v>
+        <v>-0.2972548712472474</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3776230717358686</v>
+        <v>-0.3972044904248335</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1587453846917839</v>
+        <v>-0.1608186318802325</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.09139104871929504</v>
+        <v>-0.1346422375989036</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.07081217226144787</v>
+        <v>0.03733780152644073</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.02200629056788017</v>
+        <v>0.003204085238074583</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.0837036765843493</v>
+        <v>-0.09543981591230022</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1646557542625686</v>
+        <v>0.1599792135101623</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2554505476706055</v>
+        <v>0.2333595800351205</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4927716352809668</v>
+        <v>0.4631482780867557</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5539823584936272</v>
+        <v>0.5306677111774576</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3953086985011254</v>
+        <v>0.3653443830869207</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3080</v>
+        <v>3088</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.266930922085017</v>
+        <v>-1.266169983206858</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2559091808982785</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6332465653480384</v>
+        <v>-0.6234640144260837</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7297053595835123</v>
+        <v>-0.73489188689706</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3435935705978466</v>
+        <v>-0.3332894422876009</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2081890906874051</v>
+        <v>-0.2222638717054863</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.09853599028398463</v>
+        <v>-0.10351823193173</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1590642133781799</v>
+        <v>-0.1486390182050386</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2670511418043873</v>
+        <v>-0.2503365464356904</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1330116681906546</v>
+        <v>0.1556083355324986</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2060248321855127</v>
+        <v>0.2103675643718077</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5182975237473784</v>
+        <v>0.5133952290694097</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.668334552411828</v>
+        <v>0.6685772183359546</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3607322325915305</v>
+        <v>0.3532343230242176</v>
       </c>
     </row>
     <row r="15">
@@ -2682,257 +2682,257 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2932</v>
+        <v>2940</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.205839525944072</v>
+        <v>-1.186282904316712</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1988685295825405</v>
+        <v>-0.171387382029252</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7793905151559457</v>
+        <v>-0.7506138548792833</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.95528782054717</v>
+        <v>-0.9422600844619211</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4546521063600437</v>
+        <v>-0.4276292516637739</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4294795057824601</v>
+        <v>-0.4267675941636853</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4121143291520681</v>
+        <v>-0.4010085732615991</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3501597735111801</v>
+        <v>-0.3568107318088281</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3584353644507985</v>
+        <v>-0.3597813008232222</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1386662376128598</v>
+        <v>0.1424696831356798</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.05532757001083866</v>
+        <v>0.04033535596681759</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4838162447153209</v>
+        <v>0.4725245346781861</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7308029239947302</v>
+        <v>0.7234053704400978</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4645131719795614</v>
+        <v>0.4476969785527487</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 36.07</t>
+          <t>X &gt; 36.08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2821</v>
+        <v>2829</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.855474334421281</v>
+        <v>-0.8163926999751965</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.09916926140736848</v>
+        <v>-0.05163695098882926</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8283369229873614</v>
+        <v>-0.8147105141767454</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.016245395517778</v>
+        <v>-1.019099762829903</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5455744100812083</v>
+        <v>-0.5354379344905382</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4603644539963341</v>
+        <v>-0.4746665499472229</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4389927764873889</v>
+        <v>-0.4293155720348807</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.356276035954707</v>
+        <v>-0.3651129967291737</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.36248357575586</v>
+        <v>-0.3667499168200408</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1521455363999635</v>
+        <v>0.1521776861105621</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1089926746626162</v>
+        <v>0.08937999475821101</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4113035006548813</v>
+        <v>0.3948965554446673</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7199414036670078</v>
+        <v>0.7064524097995601</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4342877093728106</v>
+        <v>0.4101485551536967</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 39.38</t>
+          <t>X &gt; 39.39</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2682</v>
+        <v>2690</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7708788558131587</v>
+        <v>-0.7283746311230601</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04005751393275148</v>
+        <v>0.009941687803426191</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9552749953420729</v>
+        <v>-0.9209050558612546</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.308321227218386</v>
+        <v>-1.291368052237623</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7856035928326648</v>
+        <v>-0.7571726672397574</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7857379306204137</v>
+        <v>-0.7817849179375571</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.647317014319448</v>
+        <v>-0.6193926800254772</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.5734500341355115</v>
+        <v>-0.5647793437545516</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5396886503318541</v>
+        <v>-0.5274025105121609</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.08271967038871963</v>
+        <v>0.09858303506690902</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.010660211761504</v>
+        <v>0.005966751099599321</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3640680232875226</v>
+        <v>0.3615312579812198</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9713471494274586</v>
+        <v>0.9700908035363511</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3982841661166248</v>
+        <v>0.3641170781911143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 42.69</t>
+          <t>X &gt; 42.7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2554</v>
+        <v>2561</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6652190371723847</v>
+        <v>-0.6192736182593066</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.02738245273918949</v>
+        <v>0.07987801663422545</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9921448867210501</v>
+        <v>-0.9560085604722488</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.096203226147132</v>
+        <v>-1.078454332552695</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7364060943541162</v>
+        <v>-0.6878601745883444</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6733155477334662</v>
+        <v>-0.6493581387838532</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4456479296470377</v>
+        <v>-0.397636250656717</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3446553912783656</v>
+        <v>-0.3168075506730261</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2669878066913327</v>
+        <v>-0.23663841830259</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3901079932419407</v>
+        <v>0.4233283933072656</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5594585955751654</v>
+        <v>0.5706131702928374</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7725630404179498</v>
+        <v>0.7849688963340284</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.118362531484372</v>
+        <v>1.131708665982622</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8577117605029301</v>
+        <v>0.8731393148000208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 46</t>
+          <t>X &gt; 46.01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2440</v>
+        <v>2447</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4171644980455866</v>
+        <v>-0.3681289607498996</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.05583412486932815</v>
+        <v>0.1107927226102206</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9519327645853437</v>
+        <v>-0.9141400057483153</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.9034403549569276</v>
+        <v>-0.8849206349206398</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6652689354330903</v>
+        <v>-0.6167230156673185</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.694825841637801</v>
+        <v>-0.670868432688188</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4934716320441481</v>
+        <v>-0.4454599530538275</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2842570368221189</v>
+        <v>-0.2574308417575679</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3636992809299784</v>
+        <v>-0.3352698178743339</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3227348792732414</v>
+        <v>0.3529571795697777</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.509512631665288</v>
+        <v>0.5166140348534611</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6899900705210413</v>
+        <v>0.6973798731582903</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.194427728850634</v>
+        <v>1.201282020153918</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.156985159991997</v>
+        <v>1.164262313309457</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2330</v>
+        <v>2337</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5767654100807817</v>
+        <v>-0.5237811969502033</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3366526902657512</v>
+        <v>0.393890577136645</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.8283369229873614</v>
+        <v>-0.788865290832959</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.126010795231267</v>
+        <v>-1.106501283147992</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8940821198288873</v>
+        <v>-0.8455362000631155</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.810657598109934</v>
+        <v>-0.7867001891603209</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9809477605425627</v>
+        <v>-0.9329360815522421</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3548223433331685</v>
+        <v>-0.32902130235491</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2210316859167776</v>
+        <v>-0.1948343051588068</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1522668670943546</v>
+        <v>0.1794543583565442</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5288826872787524</v>
+        <v>0.5315826314023937</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6733782614564063</v>
+        <v>0.6753291719337469</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.17854012590854</v>
+        <v>1.178759178617675</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.21450292541801</v>
+        <v>1.213854532716908</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2218</v>
+        <v>2224</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4125707067933462</v>
+        <v>-0.3557132611526868</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3143726965456963</v>
+        <v>0.3746051177973087</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9347152349719323</v>
+        <v>-0.8931365120143298</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.254130379153352</v>
+        <v>-1.233547351524876</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.117959500594367</v>
+        <v>-1.069413580828595</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.135333672398133</v>
+        <v>-1.11137626344852</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9052958302254481</v>
+        <v>-0.8572841512351275</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2932277833646992</v>
+        <v>-0.2439802209709825</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1495963028618803</v>
+        <v>-0.1010967149998692</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.330395219775383</v>
+        <v>0.3790315387175198</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6913809768974133</v>
+        <v>0.714459436505166</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.976640357171334</v>
+        <v>0.9974463177549566</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.393446334505612</v>
+        <v>1.411640909176739</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.284666278707725</v>
+        <v>1.30097354097628</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2109</v>
+        <v>2115</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1877718224965292</v>
+        <v>-0.1493941667188992</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.375982982784798</v>
+        <v>0.4178117040336886</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9171335556345426</v>
+        <v>-0.8953444786978082</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.070596355308595</v>
+        <v>-1.071090847686598</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.088791345756533</v>
+        <v>-1.040245425990761</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.075105259383861</v>
+        <v>-1.051147850434248</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.7342837037564109</v>
+        <v>-0.6862720247660903</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.303007193878841</v>
+        <v>-0.2537596314851243</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.006919182143633407</v>
+        <v>0.04023702651755912</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3051134677478444</v>
+        <v>0.35116021875222</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6952822703360724</v>
+        <v>0.7143956577409512</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.182981231442092</v>
+        <v>1.198094309999462</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.263974239778676</v>
+        <v>1.275749622206312</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.280091441424425</v>
+        <v>1.288387864836345</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.06653651691819107</v>
+        <v>0.1083420404496707</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2535522220561646</v>
+        <v>0.2979286548274303</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8904699119496229</v>
+        <v>-0.8674562543235851</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.00999501811151</v>
+        <v>-1.010489510489514</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6991337220563523</v>
+        <v>-0.6505878022905804</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.851310141971716</v>
+        <v>-0.8273527330221029</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4365200017373922</v>
+        <v>-0.3885083227470716</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.004487746423230021</v>
+        <v>0.04475981597048673</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2119638077710633</v>
+        <v>0.2575374565839397</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.7397561558689887</v>
+        <v>0.7823602244203087</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.213794367293637</v>
+        <v>1.22757042623487</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.777441157972127</v>
+        <v>1.785237663100261</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.586638330701795</v>
+        <v>1.589879936336636</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.041951814612716</v>
+        <v>2.038724998152198</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2276971464141866</v>
+        <v>-0.1801707429373351</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.09244723262499832</v>
+        <v>0.1403659666988517</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9997490448339121</v>
+        <v>-0.9749625551940042</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8695239012455502</v>
+        <v>-0.8700183936235533</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7103885616373731</v>
+        <v>-0.6618426418716012</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7349029440194599</v>
+        <v>-0.7109455350698468</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1221884105817708</v>
+        <v>-0.07417673159145011</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4837043190220527</v>
+        <v>0.5329518814157694</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7209685646518906</v>
+        <v>0.7642196156266223</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.404847455546751</v>
+        <v>1.442536957558417</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.768370419425025</v>
+        <v>1.774877196717611</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.747927773620042</v>
+        <v>2.745061101464472</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.682257014240818</v>
+        <v>2.671791586917813</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.778462510924605</v>
+        <v>2.7598922429246</v>
       </c>
     </row>
     <row r="25">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1751</v>
+        <v>1757</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1189353817011138</v>
+        <v>-0.0669300067051708</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4895711831747249</v>
+        <v>0.5400254731294254</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7589281469417202</v>
+        <v>-0.7327606867534442</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.742533396068211</v>
+        <v>-0.743027888446214</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5409253965173519</v>
+        <v>-0.4923794767515801</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8696185268139658</v>
+        <v>-0.8456611178643527</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.04368574436129791</v>
+        <v>0.004325934629022754</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.6844647353579418</v>
+        <v>0.7337122977516586</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9400166378480606</v>
+        <v>0.9813156704019974</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.660553876666711</v>
+        <v>1.694197391237552</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.88784861220401</v>
+        <v>1.888463318203463</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.868121113455281</v>
+        <v>2.857273197287192</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.824168141399575</v>
+        <v>2.803606448867924</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.969649585940637</v>
+        <v>2.938820918168439</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1639</v>
+        <v>1645</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.01890995150699837</v>
+        <v>0.03843186443340585</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6191440770097216</v>
+        <v>0.6729527414447176</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8090619582012408</v>
+        <v>-0.7810730708970368</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9219979088378096</v>
+        <v>-0.9224924012158127</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4876430850338025</v>
+        <v>-0.4390971652680307</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7981717909610211</v>
+        <v>-0.774214382011408</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2749794146648838</v>
+        <v>-0.2269677356745632</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.7169185068979118</v>
+        <v>0.7661660692916286</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.054881764850919</v>
+        <v>1.093935101492228</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.517358103525709</v>
+        <v>1.546702265358093</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.591327835611231</v>
+        <v>1.585722912046933</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.940670200543039</v>
+        <v>2.920485394092672</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.861477418601929</v>
+        <v>2.829278835309999</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.001497507584993</v>
+        <v>2.956743150212901</v>
       </c>
     </row>
     <row r="27">
@@ -3306,101 +3306,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.04349837572539172</v>
+        <v>0.02111762941940043</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9144854916850846</v>
+        <v>0.9725005636413755</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.666056644058088</v>
+        <v>-0.6358089918400935</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7993361118004287</v>
+        <v>-0.7998306041784318</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5471118309040364</v>
+        <v>-0.4985659111382645</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5132424125996451</v>
+        <v>-0.489285003650032</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.07094354920441504</v>
+        <v>-0.02293187021409437</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.240643933491064</v>
+        <v>1.289891495884781</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.216833818382106</v>
+        <v>1.252918886747985</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.39358201338878</v>
+        <v>1.417232598423119</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.820863578466891</v>
+        <v>1.805977526381099</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.148561287348528</v>
+        <v>3.115791167566805</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.098125654218464</v>
+        <v>3.050014005166361</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.363377735237037</v>
+        <v>3.299058867181728</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 75.79</t>
+          <t>X &gt; 75.78</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.006466810128948453</v>
+        <v>0.07981623266697824</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.9187125844047017</v>
+        <v>0.9823050424409629</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1249412805233732</v>
+        <v>-0.09221421824226184</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2110102969926828</v>
+        <v>-0.2115047893706858</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3888095833255889</v>
+        <v>-0.3402636635598171</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1635336070430569</v>
+        <v>-0.1395761980934438</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.328540460511249</v>
+        <v>0.3765521395015696</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.808119257243611</v>
+        <v>1.857366819637328</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.530842940663163</v>
+        <v>1.60410005044286</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.948414164527001</v>
+        <v>2.005938376621387</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.291011676309161</v>
+        <v>2.306484302553216</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.668277080599957</v>
+        <v>3.66241600026418</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.725276512124317</v>
+        <v>3.699846393815712</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.849981767427174</v>
+        <v>3.804695149125955</v>
       </c>
     </row>
     <row r="29">
@@ -3410,49 +3410,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4611303751345233</v>
+        <v>-0.3719539301501342</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.6482111492789784</v>
+        <v>0.7215259047719798</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2534397645239395</v>
+        <v>0.2905678298137886</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4407374002141538</v>
+        <v>-0.4412318925921568</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5668257991466206</v>
+        <v>-0.5182798793808487</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3518920003441792</v>
+        <v>-0.3279345913945662</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4702401795487674</v>
+        <v>0.5182518585390881</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.487095690749655</v>
+        <v>1.536343253143372</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.426113534226879</v>
+        <v>1.499370644006575</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.108072987552156</v>
+        <v>2.159466218179226</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.612016186708715</v>
+        <v>2.614847617304306</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.26530091855917</v>
+        <v>4.239378740489485</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.226039947601912</v>
+        <v>4.173981737256241</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.419388807804403</v>
+        <v>4.340586368438956</v>
       </c>
     </row>
     <row r="30">
@@ -3462,49 +3462,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6748323803442347</v>
+        <v>-0.5669838628016706</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.850863655869496</v>
+        <v>0.9351740880596324</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5895351053113913</v>
+        <v>-0.5459062905702652</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.409880303928354</v>
+        <v>-1.410374796306357</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.758055788582986</v>
+        <v>-1.709509868817214</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.27056769050683</v>
+        <v>-1.246610281557217</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6898788102292812</v>
+        <v>-0.6418671312389606</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.4590221277330357</v>
+        <v>0.5082696901267525</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7782681080923908</v>
+        <v>0.8515252178720871</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.599128182510292</v>
+        <v>1.643666218806146</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.020769283323084</v>
+        <v>2.009867976593249</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.063999403538951</v>
+        <v>3.018605056163473</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.368366266116361</v>
+        <v>3.288846369143371</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.746937717650887</v>
+        <v>3.632948265379262</v>
       </c>
     </row>
     <row r="31">
@@ -3514,49 +3514,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.07265914980040122</v>
+        <v>0.007050646508901082</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.068448335117417</v>
+        <v>1.118624033828873</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.01439644413304109</v>
+        <v>-0.01454983413736244</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5722446950400908</v>
+        <v>-0.5727391874180938</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.257323238961469</v>
+        <v>-2.208777319195697</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.042518016665831</v>
+        <v>-1.018560607716218</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2097971832714549</v>
+        <v>-0.1617855042811343</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.5846020628500739</v>
+        <v>0.6338496252437906</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.326372199905279</v>
+        <v>1.399629309684975</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.852600192566243</v>
+        <v>1.951947517860816</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.518063034348181</v>
+        <v>2.550559363902707</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.309663035021593</v>
+        <v>3.296799495763011</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.119397239179456</v>
+        <v>3.130999367364318</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.759137624667808</v>
+        <v>3.724080926627394</v>
       </c>
     </row>
     <row r="32">
@@ -3566,49 +3566,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.580015129633452</v>
+        <v>-1.462207633270218</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>0.02964962069179222</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7331197545994641</v>
+        <v>-0.7332731446037855</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1524441605606484</v>
+        <v>-0.1529386529386514</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.042085065007704</v>
+        <v>-1.993539145241932</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.294260584922156</v>
+        <v>-1.270303175972543</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1225305573131763</v>
+        <v>0.170542236303497</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.307113565178085</v>
+        <v>1.356361127571802</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.696581859105756</v>
+        <v>1.769838968885452</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.198014414127243</v>
+        <v>2.297361739421817</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.983175298360685</v>
+        <v>2.994122192786634</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.558589776470143</v>
+        <v>3.50273938060198</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.138438923156734</v>
+        <v>3.107581454038154</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.267789031214598</v>
+        <v>4.257527216954415</v>
       </c>
     </row>
     <row r="33">
@@ -3618,49 +3618,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.777510935757789</v>
+        <v>0.9574496963658063</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.761830460671483</v>
+        <v>2.85738373569707</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.7940253680512726</v>
+        <v>0.7938719780469512</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.373688713886821</v>
+        <v>1.373194221508818</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3859609585439401</v>
+        <v>0.4345068783097119</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.9080540893026239</v>
+        <v>0.9320114982522369</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.17165833677803</v>
+        <v>2.219670015768351</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.502342501980053</v>
+        <v>3.551590064373769</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.542483940962896</v>
+        <v>2.615741050742592</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.591441549127417</v>
+        <v>2.69078887442199</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.518838781392581</v>
+        <v>2.4866484268859</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.168981682695495</v>
+        <v>5.016725276610345</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.297363560759067</v>
+        <v>4.172129147799332</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.877501016854666</v>
+        <v>5.769488616556274</v>
       </c>
     </row>
     <row r="34">
@@ -3670,49 +3670,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3573639069822363</v>
+        <v>-0.3865597013348676</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.120253088757032</v>
+        <v>1.119066302312376</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.497682476202762</v>
+        <v>1.49752908619844</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.302594310710802</v>
+        <v>-0.303088803088805</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.0686830916057275</v>
+        <v>-0.02013717183995567</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.386992096330516</v>
+        <v>1.410949505280129</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.618884053666662</v>
+        <v>3.666895732656982</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.696216954281475</v>
+        <v>4.745464516675192</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.318632481156378</v>
+        <v>2.391889590936074</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.240914457027287</v>
+        <v>2.340261782321861</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.7117991836553088</v>
+        <v>0.5917197903842322</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.071758731359473</v>
+        <v>2.966488844351446</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.426801676495671</v>
+        <v>3.343531689988389</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.202924923621431</v>
+        <v>5.136978096405301</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>10.61432206470374</v>
+        <v>10.58512627035111</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>9.003135971639914</v>
+        <v>9.001949185195258</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.4047619047619051</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.945895203959722</v>
+        <v>7.995142766353439</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.252896809620111</v>
+        <v>-3.784084585420139</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3959391740605156</v>
+        <v>-0.154489276626677</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.433850233469769</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>5.020801079407363</v>
+        <v>4.461302420729616</v>
       </c>
     </row>
   </sheetData>
@@ -3904,261 +3904,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 2.983</t>
+          <t>X &lt; 2.991</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.270106704889322</v>
+        <v>1.318118383879643</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.400801238277339</v>
+        <v>-6.327544128497642</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.679291463178622</v>
+        <v>-3.579944137884048</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-2.693516430962632</v>
+        <v>-2.593608394943956</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.849614469083491</v>
+        <v>-3.725917848055246</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.460241512873097</v>
+        <v>-5.311551965095269</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.805934434075141</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 6.292</t>
+          <t>X &lt; 6.3</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>174</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.863911555672544</v>
+        <v>7.834715761319913</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.655024313183432</v>
+        <v>1.653837526738776</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.834965572106547</v>
+        <v>1.834812182102226</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.539903359373078</v>
+        <v>2.539408866995075</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.170799986826069</v>
+        <v>-3.122254067060297</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.022851244547297</v>
+        <v>-3.998893835597684</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.532848960135311</v>
+        <v>-3.484837281144991</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.99991760392205</v>
+        <v>-3.950670041528333</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.63561240412298</v>
+        <v>-4.562355294343284</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.76139326941837</v>
+        <v>-3.662045944123797</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.966094427678563</v>
+        <v>-3.866186391659888</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.3799921373922</v>
+        <v>-7.256295516363956</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-7.225430347027448</v>
+        <v>-7.07674079924962</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.723832627835399</v>
+        <v>-8.551833868268737</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 9.601</t>
+          <t>X &lt; 9.608</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>283</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.529684676179428</v>
+        <v>6.500488881826797</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.738286568981323</v>
+        <v>1.737099782536667</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.756942746063736</v>
+        <v>2.756789356059414</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.887167889652098</v>
+        <v>2.886673397274095</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.995521446097051</v>
+        <v>2.044067365862823</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1727541329759461</v>
+        <v>0.1967115419255592</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.618670007208955</v>
+        <v>-0.5706583282186344</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.085738650995694</v>
+        <v>-1.036491088601977</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.9734205352377217</v>
+        <v>1.046677645017418</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4768586293672286</v>
+        <v>0.5762059546618019</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6255143615664025</v>
+        <v>0.7254223975850778</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.106891938375099</v>
+        <v>-0.9831953173468548</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.527042791688508</v>
+        <v>-1.378353243910681</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.301307141461976</v>
+        <v>-1.129308381895314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 12.91</t>
+          <t>X &lt; 12.92</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.591373126092158</v>
+        <v>5.523461316599821</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.81151233423315</v>
+        <v>1.782010850149007</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.621560226586539</v>
+        <v>2.587313629220397</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.474676936439955</v>
+        <v>3.436622130866724</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.90024280503102</v>
+        <v>3.906605603823685</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.26990599129261</v>
+        <v>2.157162751493374</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2574847886529383</v>
+        <v>0.4138143545756137</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5133077111312616</v>
+        <v>0.6691354403461176</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.657144831716927</v>
+        <v>1.834085908132394</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.530117601652123</v>
+        <v>1.731411173471251</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8434887325485576</v>
+        <v>1.046501495165934</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.049843958469609</v>
+        <v>-0.818408690546093</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.229030956361335</v>
+        <v>-0.9731820017253057</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.244259161556485</v>
+        <v>-0.9645217550945517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 16.22</t>
+          <t>X &lt; 16.23</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.399817914419778</v>
+        <v>4.449595134819972</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.238173105759614</v>
+        <v>2.316967500213572</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.760832913665134</v>
+        <v>2.83898042764978</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.542434204042479</v>
+        <v>4.617216117216117</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.004144650946785</v>
+        <v>4.127966976264197</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.73271134113233</v>
+        <v>1.756668750081943</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2809610466260182</v>
+        <v>0.228122752599603</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.002284067748959728</v>
+        <v>-0.05422376925162808</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4882043639635611</v>
+        <v>0.4592623372079032</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3735796852807525</v>
+        <v>0.3693787105213602</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.352702056432328</v>
+        <v>0.3487245015173883</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.8996844970946967</v>
+        <v>-0.8775124308425006</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.319835350408106</v>
+        <v>-1.272670357406327</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.277923229593341</v>
+        <v>-1.207111733923064</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.530814174744236</v>
+        <v>3.630239052305996</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.148720196519299</v>
+        <v>2.047061967150142</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.488163202366309</v>
+        <v>2.530516961291582</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.205759858436316</v>
+        <v>3.245196324143691</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.667470305340622</v>
+        <v>2.755947183191772</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.496415553771598</v>
+        <v>1.50252822057773</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5646271886681049</v>
+        <v>-0.6079082493212198</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5905193618666118</v>
+        <v>-0.7012683494125227</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2308514227870901</v>
+        <v>0.1415244373451117</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.03083207942512445</v>
+        <v>-0.09579387954025265</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.205643232902915</v>
+        <v>0.2865759368532892</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.377625673565284</v>
+        <v>-1.268160551588281</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.062482409231635</v>
+        <v>-0.9954202260560407</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8367467590051021</v>
+        <v>-0.7463753640406736</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.307261309367128</v>
+        <v>3.372241116289487</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.518255459632393</v>
+        <v>1.54396599191795</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.986616010758986</v>
+        <v>2.008071140858142</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.803845462395635</v>
+        <v>2.87324929971988</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.648271958682656</v>
+        <v>1.526157021513065</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3407077167128065</v>
+        <v>0.2730192875953179</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1705313550318124</v>
+        <v>-0.2784343476424169</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3512751556932017</v>
+        <v>0.1824599536706231</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6611211821123177</v>
+        <v>0.5140377130841927</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1887976142175418</v>
+        <v>-0.1869407448806584</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5171081667916937</v>
+        <v>-0.5684810008128665</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.224386380320183</v>
+        <v>-1.248321643521777</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.273709050691686</v>
+        <v>-1.329614362468014</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.8007546118372204</v>
+        <v>-0.7111113723738285</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.404555867662893</v>
+        <v>3.443523580803223</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6849679400960866</v>
+        <v>0.7012316379023673</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9271392305002806</v>
+        <v>0.9397381174485702</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.328792655426426</v>
+        <v>1.385744392593701</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5779632511086277</v>
+        <v>0.5803730177113309</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4502575782995066</v>
+        <v>0.5951698920321604</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.001423183661849237</v>
+        <v>0.1125728745366672</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1698060448918426</v>
+        <v>0.2325340269759479</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6407387819860801</v>
+        <v>0.6768855503506401</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2091800143437794</v>
+        <v>-0.1937007516406695</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5202641513273676</v>
+        <v>-0.4446979833216815</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.33694982875928</v>
+        <v>-1.233988873075432</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.544334724625884</v>
+        <v>-1.464912567024264</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.999450138229129</v>
+        <v>-0.8977340888901324</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.489913504561358</v>
+        <v>3.478998882917004</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8349051756718922</v>
+        <v>0.8068925781604364</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.71750605369057</v>
+        <v>1.683572012713235</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.081707799618705</v>
+        <v>2.085688358828094</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.9954730410435602</v>
+        <v>0.9612305064424191</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7040814499829366</v>
+        <v>0.7397450193617416</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4869846729109284</v>
+        <v>0.4974358874478284</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.66035518740415</v>
+        <v>0.6271773983880706</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.056829572509919</v>
+        <v>1.004879286728325</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.06756314879707048</v>
+        <v>-0.1321169195650285</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.272264307057263</v>
+        <v>-0.2853651341026975</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.152799237959023</v>
+        <v>-1.138775424996695</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.572950091272432</v>
+        <v>-1.575020856301386</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.706775282765939</v>
+        <v>-0.6872898628991564</v>
       </c>
     </row>
     <row r="15">
@@ -4376,257 +4376,257 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.78012814617248</v>
+        <v>2.72569952603228</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.570277297623683</v>
+        <v>0.5030340316038462</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.783222954669291</v>
+        <v>1.708017066470596</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.280519776828065</v>
+        <v>2.237581363480643</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.09862604030517</v>
+        <v>1.028907762097063</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.1190222631433</v>
+        <v>1.10639352072414</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.159788605046643</v>
+        <v>1.125737431498685</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.015040670365465</v>
+        <v>1.024804591051286</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.115218868395473</v>
+        <v>1.112932061978547</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.05702063703995464</v>
+        <v>-0.06675056855576145</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1411790910818098</v>
+        <v>0.1752519581860668</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8719850611559465</v>
+        <v>-0.8458260523008008</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.453296269022132</v>
+        <v>-1.437719473899435</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.8246597324136502</v>
+        <v>-0.7867453514339076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 36.07</t>
+          <t>X &lt; 36.08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.722623792474501</v>
+        <v>1.635155966749117</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2990417878409275</v>
+        <v>0.1987140246600276</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.675488115263022</v>
+        <v>1.63916532467988</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.142613082797915</v>
+        <v>2.135887223561468</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.161192067368397</v>
+        <v>1.13306508187587</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.056538107339939</v>
+        <v>1.079844328359975</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.08695652173914</v>
+        <v>1.060079826796269</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.9157458661180797</v>
+        <v>0.929316435821228</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.002692703678136</v>
+        <v>1.007155755871118</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.06911958377597927</v>
+        <v>-0.06988031854188392</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.02203724612951419</v>
+        <v>0.0619342937601175</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6092650748879507</v>
+        <v>-0.5758967776801995</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.251309419325622</v>
+        <v>-1.225275388043791</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6557512838919806</v>
+        <v>-0.6072268359915185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 39.38</t>
+          <t>X &lt; 39.39</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.329244397273136</v>
+        <v>1.249036545039829</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.155389515197804</v>
+        <v>0.06506105669036089</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.671091685756551</v>
+        <v>1.600797452939872</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.37476489712396</v>
+        <v>2.329483889364127</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.43459992540803</v>
+        <v>1.374499552138083</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.501631822230294</v>
+        <v>1.484982069326009</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.320408515754515</v>
+        <v>1.261806718640592</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.188685277735715</v>
+        <v>1.16657133778201</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.194772202366522</v>
+        <v>1.167134863846456</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.07657708142231456</v>
+        <v>0.04711416207144481</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2072213289300606</v>
+        <v>0.2143885513295487</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4290913302504933</v>
+        <v>-0.4250520471894532</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.519932995099794</v>
+        <v>-1.518750563598211</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4893683710301957</v>
+        <v>-0.429690120865331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 42.69</t>
+          <t>X &lt; 42.7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9960070463887263</v>
+        <v>0.9212607241326225</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.033513639948616</v>
+        <v>-0.04917126298401797</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.520520206988735</v>
+        <v>1.456600552622852</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.746927467540935</v>
+        <v>1.709033613445378</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.181558072268999</v>
+        <v>1.097235452885613</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.143176852515282</v>
+        <v>1.097760780074239</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.8458295202662427</v>
+        <v>0.7645104376336604</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6875934892034081</v>
+        <v>0.6396222892860024</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.626611332680632</v>
+        <v>0.575462774509262</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.408607031283573</v>
+        <v>-0.4599745766114793</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.675074712088545</v>
+        <v>-0.6914822308251658</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.011295695001913</v>
+        <v>-1.029947152084553</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.554979593404873</v>
+        <v>-1.575919781187217</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.143944375544002</v>
+        <v>-1.16980399595905</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 46</t>
+          <t>X &lt; 46.01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5380603926973961</v>
+        <v>0.4681241430397094</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.00694677262004717</v>
+        <v>-0.08412510706460097</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.298964142769407</v>
+        <v>1.240349963039939</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.288512925557718</v>
+        <v>1.255686467026671</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.955206174358473</v>
+        <v>0.8809848633027002</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.054108545453893</v>
+        <v>1.013786070867411</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8284008823410289</v>
+        <v>0.755645688379424</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5344424520568865</v>
+        <v>0.4937084576902109</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7042739135375768</v>
+        <v>0.6608654718522615</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2610516917940231</v>
+        <v>-0.3032285119438427</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5234562545550787</v>
+        <v>-0.5328530583265518</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7775951247040851</v>
+        <v>-0.7877212928374178</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.486263000521816</v>
+        <v>-1.496274415640507</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.433637563797888</v>
+        <v>-1.445844548593513</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6829563329053485</v>
+        <v>0.6148881751130162</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3583358898319489</v>
+        <v>-0.4294958065945593</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.008524434256415</v>
+        <v>0.9547834464700529</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.439667994931781</v>
+        <v>1.407943349753694</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.148422515743789</v>
+        <v>1.080332139836258</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.096579278802736</v>
+        <v>1.059816701317139</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.367644363468756</v>
+        <v>1.298855015101708</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5750195612446873</v>
+        <v>0.5394081789404908</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4597780449823574</v>
+        <v>0.4244871375724983</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.01032523317061873</v>
+        <v>-0.04517528706982432</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4863231901285801</v>
+        <v>-0.4893612906968556</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6689824767314789</v>
+        <v>-0.67149975848303</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.306170769003117</v>
+        <v>-1.307222960766261</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.351731917474353</v>
+        <v>-1.353145719111048</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4242827462240584</v>
+        <v>0.3593650669362773</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2930200226292854</v>
+        <v>-0.3604295905913375</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.023330573279431</v>
+        <v>0.9725972763504345</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.43712396805801</v>
+        <v>1.407204527316253</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.284837363038328</v>
+        <v>1.222678596115479</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.355425381064265</v>
+        <v>1.320702463813582</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.145946611404071</v>
+        <v>1.085107029871843</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4516801266244457</v>
+        <v>0.3932922601285682</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.339547074960997</v>
+        <v>0.2827793902228208</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2034663505248702</v>
+        <v>-0.2582488609952946</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6127710893477243</v>
+        <v>-0.6377827636216367</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9364492029770517</v>
+        <v>-0.959061870190105</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.407750951431133</v>
+        <v>-1.428086289176768</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.284317091485924</v>
+        <v>-1.30400370171936</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2064</v>
+        <v>2069</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1113407965656421</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3239861815691967</v>
+        <v>-0.3655351822891149</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9022033403659648</v>
+        <v>0.8761284647978158</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.10756826966454</v>
+        <v>1.102212602212603</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.12828414309736</v>
+        <v>1.072761033666524</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.162358667437658</v>
+        <v>1.131737767233538</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.8625199413703584</v>
+        <v>0.8088973544273941</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4223625350782143</v>
+        <v>0.3697841891876266</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1675819289430365</v>
+        <v>0.1184769028657158</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1493911309527149</v>
+        <v>-0.1963041406405779</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5478907388253091</v>
+        <v>-0.5665813679169247</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.046458322904094</v>
+        <v>-1.060998669374605</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.127461889395796</v>
+        <v>-1.139709314991755</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.14397430118477</v>
+        <v>-1.153901611584132</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2177</v>
+        <v>2182</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.137849051164352</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1754736306985052</v>
+        <v>-0.2155516837654687</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.7835206254689595</v>
+        <v>0.7593234666059629</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9390875361980022</v>
+        <v>0.9348279457768456</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6555207977357753</v>
+        <v>0.6077385359079628</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8407105495900495</v>
+        <v>0.8145213746054196</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5059718498453663</v>
+        <v>0.4593875000231193</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.110188574040869</v>
+        <v>0.06443849195630236</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.04266312772764991</v>
+        <v>-0.08448449037627626</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.52510374307451</v>
+        <v>-0.5629093276196002</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.9594787644490737</v>
+        <v>-0.9705289572192086</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.476317883568264</v>
+        <v>-1.482328104465516</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.299316692784295</v>
+        <v>-1.302761091897615</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.716667859278012</v>
+        <v>-1.715861387048299</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2315</v>
+        <v>2320</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1461296197671089</v>
+        <v>0.1079139261859794</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.02058122743273572</v>
+        <v>-0.05895414609433658</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.7717471813019472</v>
+        <v>0.7490246037883779</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.7101907900432565</v>
+        <v>0.7072348252605707</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.583923169283544</v>
+        <v>0.542186791085129</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.6462859175578757</v>
+        <v>0.6239880224423615</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1968276523356565</v>
+        <v>0.1573145694445444</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2897316601768622</v>
+        <v>-0.3279543142672878</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4371069052525556</v>
+        <v>-0.4704012713547883</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9846498916472086</v>
+        <v>-1.012531630712509</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.275744138460311</v>
+        <v>-1.279113591426338</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.062100327357697</v>
+        <v>-2.058635948215219</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.007089193630065</v>
+        <v>-1.999658487325014</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.08372935333874</v>
+        <v>-2.071948810797473</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2422</v>
+        <v>2427</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.05099010367726464</v>
+        <v>0.01348275861732162</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3029752702209123</v>
+        <v>-0.3386725784876461</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5193069613624743</v>
+        <v>0.4986111812485277</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5485453697775995</v>
+        <v>0.5464271059264831</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4040311543043984</v>
+        <v>0.3670726981285313</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6829641645798148</v>
+        <v>0.662533151114296</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1258148981955358</v>
+        <v>0.09047038137542529</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4012008598993546</v>
+        <v>-0.4350727230482434</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5447593995765345</v>
+        <v>-0.5729232011793499</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.064372663288729</v>
+        <v>-1.086359291358029</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.227785629971713</v>
+        <v>-1.226765361434254</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.936594926006151</v>
+        <v>-1.928195877422624</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.902575671970268</v>
+        <v>-1.88917807319914</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.007145554361401</v>
+        <v>-1.988459189724203</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2534</v>
+        <v>2539</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.02125447996370866</v>
+        <v>-0.05816988687207214</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3519446432832183</v>
+        <v>-0.3859526997642959</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4954029784526028</v>
+        <v>0.475703584184636</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6078906423273338</v>
+        <v>0.6055876253993162</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3277660632194568</v>
+        <v>0.2948952860496448</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5680512537303741</v>
+        <v>0.5500684323849256</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2684160878140815</v>
+        <v>0.2361223490163624</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3742836963296767</v>
+        <v>-0.4046139929318144</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5536557502478772</v>
+        <v>-0.5773195103484952</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.8510883587324329</v>
+        <v>-0.8684859801026548</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8979363204653907</v>
+        <v>-0.8935971552002187</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.771214048141644</v>
+        <v>-1.758188607598747</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.717805311873356</v>
+        <v>-1.698878549272244</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.807776054701286</v>
+        <v>-1.782719410137425</v>
       </c>
     </row>
     <row r="27">
@@ -5000,101 +5000,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2661</v>
+        <v>2666</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.00715291209358071</v>
+        <v>-0.04374411188250349</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4738044108122779</v>
+        <v>-0.5058449638545</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3518361690661322</v>
+        <v>0.3336009043330392</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4651152374865504</v>
+        <v>0.4634849455477195</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.322779799857166</v>
+        <v>0.2937949177930648</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.340475916506044</v>
+        <v>0.3254211946209296</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1261404782784581</v>
+        <v>0.09824771956452594</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6209700990949827</v>
+        <v>-0.6465025145134007</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5692126840281375</v>
+        <v>-0.5882098324430203</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6675343364271313</v>
+        <v>-0.6799976424319425</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9098153518838714</v>
+        <v>-0.900893092262379</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.66461420065594</v>
+        <v>-1.646600363940166</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.633806767610849</v>
+        <v>-1.608889797866176</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.783869689349743</v>
+        <v>-1.751858012235765</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 75.79</t>
+          <t>X &lt; 75.78</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2791</v>
+        <v>2797</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.03361342246004284</v>
+        <v>-0.06978407283853016</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4109012658426394</v>
+        <v>-0.4417035876345707</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.03582938760673926</v>
+        <v>0.0195637678341285</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1140240243624717</v>
+        <v>0.1138225863911657</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2034520642503566</v>
+        <v>0.1785545450270973</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1268455605934378</v>
+        <v>0.1144505617223643</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.08148656399718845</v>
+        <v>-0.1050186312687842</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8155320030262203</v>
+        <v>-0.8368059960270031</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6420699421042642</v>
+        <v>-0.6759687231749112</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8470586058651577</v>
+        <v>-0.8734277576796998</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.015930312315966</v>
+        <v>-1.022179823515387</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.698141196148384</v>
+        <v>-1.694580125399206</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.724168079558531</v>
+        <v>-1.712893059073963</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.785068043807094</v>
+        <v>-1.76603298965906</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2965</v>
+        <v>2971</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1595145110061722</v>
+        <v>0.123232690376355</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2226539405564552</v>
+        <v>-0.2522959546587344</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1280717581007806</v>
+        <v>-0.1428470929231196</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2414716476497176</v>
+        <v>0.2207220958649572</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1868026885939429</v>
+        <v>0.1763095999453625</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1153716522776165</v>
+        <v>-0.1345983643374495</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5303273821752086</v>
+        <v>-0.5485333537418953</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4717078471266163</v>
+        <v>-0.499971163827901</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7482708255812653</v>
+        <v>-0.7676192079120625</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9529719838414579</v>
+        <v>-0.9532010551418608</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.626856900626095</v>
+        <v>-1.616456505496032</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.60855918732905</v>
+        <v>-1.589511331883706</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.686364852448222</v>
+        <v>-1.658570637884601</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3126</v>
+        <v>3132</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1993647607866436</v>
+        <v>0.1633445723122549</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.274065485472498</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1746846014807559</v>
+        <v>0.1596949348696981</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4820613126544941</v>
+        <v>0.480540147312901</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6002697498710745</v>
+        <v>0.5818155791099358</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4679522511161736</v>
+        <v>0.4582406544821112</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3049380287231997</v>
+        <v>0.28768709699726</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.08058689511592121</v>
+        <v>-0.09690858573615202</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1559424502323736</v>
+        <v>-0.1801026845946154</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4300455075986989</v>
+        <v>-0.4443148861833706</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5707671393073852</v>
+        <v>-0.5669508419706091</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9202661462610848</v>
+        <v>-0.9058491696585591</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.020519366816977</v>
+        <v>-0.9961232720732127</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.146671112623714</v>
+        <v>-1.11249798065699</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3304</v>
+        <v>3312</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.006564793358734278</v>
+        <v>-0.02741546617497193</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2436264218173179</v>
+        <v>-0.256394537487914</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.01827447453679554</v>
+        <v>-0.0181734526759314</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1586038249059314</v>
+        <v>0.1582093403285398</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.6035515081213276</v>
+        <v>0.5887179085598433</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.3132853109283573</v>
+        <v>0.3059115930133061</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1242553776595088</v>
+        <v>0.1111426740416164</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.08432928377912674</v>
+        <v>-0.09708146511130167</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2496474918422891</v>
+        <v>-0.2682105367552481</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3870214538133112</v>
+        <v>-0.4120424778231637</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5614654259918055</v>
+        <v>-0.5692601941251638</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.7691447622900398</v>
+        <v>-0.7658925585188001</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7185143135187815</v>
+        <v>-0.7217685721123601</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.886241133025905</v>
+        <v>-0.8785871582903866</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3509</v>
+        <v>3518</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2747657876474676</v>
+        <v>0.2527105043847655</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.04259523360557438</v>
+        <v>0.02969210440885206</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1180156332044788</v>
+        <v>0.1176769837620384</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0363001709189561</v>
+        <v>0.03628117913832085</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3951644712179458</v>
+        <v>0.3846825695264258</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2815257277062528</v>
+        <v>0.2760815524881934</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.04168705017484342</v>
+        <v>0.03240409816535106</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1820784449362165</v>
+        <v>-0.1909012312683132</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2274093302612883</v>
+        <v>-0.2406728202241126</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3211381762301286</v>
+        <v>-0.339090726672886</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4688755065210728</v>
+        <v>-0.4706319677925777</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5769069240888598</v>
+        <v>-0.5670975017349065</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4968715495031333</v>
+        <v>-0.4917979765433316</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7111034552316156</v>
+        <v>-0.7100611787181137</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3730</v>
+        <v>3739</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1152384042312207</v>
+        <v>-0.136778491553649</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2953106797479137</v>
+        <v>-0.3066222433761681</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1140465492732545</v>
+        <v>-0.1136935650242137</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1565413556690842</v>
+        <v>-0.1560225583965291</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.03810088280569346</v>
+        <v>-0.04383063203288629</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.07400928437107979</v>
+        <v>-0.07667560124009043</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1976691604769059</v>
+        <v>-0.2028690821158321</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3555560674969058</v>
+        <v>-0.3604424583906649</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2143432637132818</v>
+        <v>-0.2225380234915306</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2188719255886724</v>
+        <v>-0.2301992172067315</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2092108116087772</v>
+        <v>-0.2056569556830539</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5231713516435903</v>
+        <v>-0.5067633057250873</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4191443986052548</v>
+        <v>-0.4057714710794826</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6072876831495648</v>
+        <v>-0.5963906217187045</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3915</v>
+        <v>3925</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.001895275806361951</v>
+        <v>0.003854655559941023</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04217853725075571</v>
+        <v>-0.04198080742663279</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.117446756760863</v>
+        <v>-0.117108199170552</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.02663400016888318</v>
+        <v>0.02659284806679807</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.01202104211905919</v>
+        <v>0.008717305413092902</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.05906312330961327</v>
+        <v>-0.06051214924788439</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1808715440996451</v>
+        <v>-0.1836013274026413</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2513837076049015</v>
+        <v>-0.2540001876992122</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.06870728816859639</v>
+        <v>-0.07345470646928476</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.06228570222187813</v>
+        <v>-0.0688120189636976</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.03929185314733274</v>
+        <v>0.0467756609187191</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1161936052056518</v>
+        <v>-0.1099259967692774</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1389710230632843</v>
+        <v>-0.1342237745220487</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2563996776438273</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4090</v>
+        <v>4100</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2381076443812589</v>
+        <v>-0.2368319804911678</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1540382367413144</v>
+        <v>-0.1536001940895346</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1698003376215098</v>
+        <v>-0.1693426366207404</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.0019277011883716</v>
+        <v>-0.001911713590551756</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.03891058745547582</v>
+        <v>-0.03986972990301041</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04545258727355161</v>
+        <v>-0.04585574899347478</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.0191883099916339</v>
+        <v>-0.02018903550886364</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1066078485433266</v>
+        <v>-0.1074017097906435</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.0412626415002677</v>
+        <v>0.03954594748402229</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.05996138430779041</v>
+        <v>0.05762199968209103</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1484437100446598</v>
+        <v>0.159603540573606</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.07441848720753086</v>
+        <v>0.08523118493678083</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1324648925930276</v>
+        <v>0.1426926442334704</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.01911408246260038</v>
+        <v>-0.009080854531696048</v>
       </c>
     </row>
   </sheetData>
